--- a/SpaceDebris_site_1000/unknown_ORS-3_attached_to_Minotaur_fourth_stage_.xlsx
+++ b/SpaceDebris_site_1000/unknown_ORS-3_attached_to_Minotaur_fourth_stage_.xlsx
@@ -452,7002 +452,7002 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96.17</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="B2" t="n">
-        <v>37373</v>
+        <v>38531</v>
       </c>
       <c r="C2" t="n">
-        <v>95.56</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>12857</v>
+        <v>10344</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>93.59</v>
+        <v>0.09</v>
       </c>
       <c r="B3" t="n">
-        <v>30916</v>
+        <v>36449</v>
       </c>
       <c r="C3" t="n">
-        <v>97.5</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>10225</v>
+        <v>10007</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112.06</v>
+        <v>0.28</v>
       </c>
       <c r="B4" t="n">
-        <v>25358</v>
+        <v>37902</v>
       </c>
       <c r="C4" t="n">
-        <v>111.57</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>13585</v>
+        <v>13963</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>79.47</v>
+        <v>0.63</v>
       </c>
       <c r="B5" t="n">
-        <v>23592</v>
+        <v>37348</v>
       </c>
       <c r="C5" t="n">
-        <v>78.98</v>
+        <v>9.57</v>
       </c>
       <c r="D5" t="n">
-        <v>15608</v>
+        <v>24593</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122.62</v>
+        <v>1.26</v>
       </c>
       <c r="B6" t="n">
-        <v>23608</v>
+        <v>36914</v>
       </c>
       <c r="C6" t="n">
-        <v>121.02</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>11856</v>
+        <v>25672</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>102.07</v>
+        <v>1.81</v>
       </c>
       <c r="B7" t="n">
-        <v>49257</v>
+        <v>36836</v>
       </c>
       <c r="C7" t="n">
-        <v>100.73</v>
+        <v>8.9</v>
       </c>
       <c r="D7" t="n">
-        <v>10955</v>
+        <v>15130</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>61.42</v>
+        <v>2.01</v>
       </c>
       <c r="B8" t="n">
-        <v>26116</v>
+        <v>35892</v>
       </c>
       <c r="C8" t="n">
-        <v>61.64</v>
+        <v>2.6</v>
       </c>
       <c r="D8" t="n">
-        <v>14158</v>
+        <v>13019</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>96.63</v>
+        <v>2.08</v>
       </c>
       <c r="B9" t="n">
-        <v>37508</v>
+        <v>34639</v>
       </c>
       <c r="C9" t="n">
-        <v>99.73</v>
+        <v>6.81</v>
       </c>
       <c r="D9" t="n">
-        <v>20023</v>
+        <v>11821</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>99.3</v>
+        <v>2.42</v>
       </c>
       <c r="B10" t="n">
-        <v>42617</v>
+        <v>36463</v>
       </c>
       <c r="C10" t="n">
-        <v>98.26000000000001</v>
+        <v>0.25</v>
       </c>
       <c r="D10" t="n">
-        <v>13038</v>
+        <v>10152</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>114.42</v>
+        <v>2.54</v>
       </c>
       <c r="B11" t="n">
-        <v>20773</v>
+        <v>37022</v>
       </c>
       <c r="C11" t="n">
-        <v>116.65</v>
+        <v>9.75</v>
       </c>
       <c r="D11" t="n">
-        <v>12079</v>
+        <v>12271</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113.05</v>
+        <v>2.57</v>
       </c>
       <c r="B12" t="n">
-        <v>27261</v>
+        <v>36230</v>
       </c>
       <c r="C12" t="n">
-        <v>111.98</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>23203</v>
+        <v>21522</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>104.02</v>
+        <v>2.64</v>
       </c>
       <c r="B13" t="n">
-        <v>47168</v>
+        <v>35929</v>
       </c>
       <c r="C13" t="n">
-        <v>103.53</v>
+        <v>0.44</v>
       </c>
       <c r="D13" t="n">
-        <v>27347</v>
+        <v>21638</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>105.99</v>
+        <v>3.58</v>
       </c>
       <c r="B14" t="n">
-        <v>44519</v>
+        <v>34636</v>
       </c>
       <c r="C14" t="n">
-        <v>109.04</v>
+        <v>6.65</v>
       </c>
       <c r="D14" t="n">
-        <v>16055</v>
+        <v>14085</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113.17</v>
+        <v>4.11</v>
       </c>
       <c r="B15" t="n">
-        <v>25419</v>
+        <v>37015</v>
       </c>
       <c r="C15" t="n">
-        <v>113.95</v>
+        <v>7.6</v>
       </c>
       <c r="D15" t="n">
-        <v>16598</v>
+        <v>12993</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>111.88</v>
+        <v>4.63</v>
       </c>
       <c r="B16" t="n">
-        <v>26625</v>
+        <v>35237</v>
       </c>
       <c r="C16" t="n">
-        <v>113.85</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>26998</v>
+        <v>13746</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>99.23</v>
+        <v>5.01</v>
       </c>
       <c r="B17" t="n">
-        <v>41802</v>
+        <v>35203</v>
       </c>
       <c r="C17" t="n">
-        <v>99.86</v>
+        <v>14.77</v>
       </c>
       <c r="D17" t="n">
-        <v>18693</v>
+        <v>14878</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>108.61</v>
+        <v>5.25</v>
       </c>
       <c r="B18" t="n">
-        <v>36151</v>
+        <v>35574</v>
       </c>
       <c r="C18" t="n">
-        <v>106.98</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>15607</v>
+        <v>14204</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>102.8</v>
+        <v>5.6</v>
       </c>
       <c r="B19" t="n">
-        <v>46520</v>
+        <v>34094</v>
       </c>
       <c r="C19" t="n">
-        <v>102.59</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="D19" t="n">
-        <v>25449</v>
+        <v>17279</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>85.7</v>
+        <v>6.18</v>
       </c>
       <c r="B20" t="n">
-        <v>23802</v>
+        <v>34294</v>
       </c>
       <c r="C20" t="n">
-        <v>87.23999999999999</v>
+        <v>12.82</v>
       </c>
       <c r="D20" t="n">
-        <v>28700</v>
+        <v>25580</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113.5</v>
+        <v>6.85</v>
       </c>
       <c r="B21" t="n">
-        <v>22738</v>
+        <v>33995</v>
       </c>
       <c r="C21" t="n">
-        <v>110.53</v>
+        <v>4.21</v>
       </c>
       <c r="D21" t="n">
-        <v>28333</v>
+        <v>12985</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>111.15</v>
+        <v>7</v>
       </c>
       <c r="B22" t="n">
-        <v>30865</v>
+        <v>33696</v>
       </c>
       <c r="C22" t="n">
-        <v>114.96</v>
+        <v>16.46</v>
       </c>
       <c r="D22" t="n">
-        <v>17552</v>
+        <v>13568</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>106.19</v>
+        <v>7.18</v>
       </c>
       <c r="B23" t="n">
-        <v>45057</v>
+        <v>33081</v>
       </c>
       <c r="C23" t="n">
-        <v>106.27</v>
+        <v>15.9</v>
       </c>
       <c r="D23" t="n">
-        <v>22539</v>
+        <v>24532</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>90.79000000000001</v>
+        <v>7.49</v>
       </c>
       <c r="B24" t="n">
-        <v>21943</v>
+        <v>30059</v>
       </c>
       <c r="C24" t="n">
-        <v>93.78</v>
+        <v>14.6</v>
       </c>
       <c r="D24" t="n">
-        <v>14670</v>
+        <v>29287</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>92.47</v>
+        <v>7.63</v>
       </c>
       <c r="B25" t="n">
-        <v>25334</v>
+        <v>32933</v>
       </c>
       <c r="C25" t="n">
-        <v>90.66</v>
+        <v>8</v>
       </c>
       <c r="D25" t="n">
-        <v>26810</v>
+        <v>17658</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>111.44</v>
+        <v>7.87</v>
       </c>
       <c r="B26" t="n">
-        <v>27466</v>
+        <v>32912</v>
       </c>
       <c r="C26" t="n">
-        <v>108.38</v>
+        <v>12.72</v>
       </c>
       <c r="D26" t="n">
-        <v>23259</v>
+        <v>13637</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>114.93</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="B27" t="n">
-        <v>24759</v>
+        <v>31218</v>
       </c>
       <c r="C27" t="n">
-        <v>115.15</v>
+        <v>10.56</v>
       </c>
       <c r="D27" t="n">
-        <v>16715</v>
+        <v>12919</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>102.36</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="B28" t="n">
-        <v>46266</v>
+        <v>32006</v>
       </c>
       <c r="C28" t="n">
-        <v>102.23</v>
+        <v>18.91</v>
       </c>
       <c r="D28" t="n">
-        <v>22607</v>
+        <v>25152</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>99.59</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="B29" t="n">
-        <v>44866</v>
+        <v>32446</v>
       </c>
       <c r="C29" t="n">
-        <v>101.45</v>
+        <v>14.92</v>
       </c>
       <c r="D29" t="n">
-        <v>15763</v>
+        <v>18271</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>103.98</v>
+        <v>9.27</v>
       </c>
       <c r="B30" t="n">
-        <v>49489</v>
+        <v>30791</v>
       </c>
       <c r="C30" t="n">
-        <v>107.18</v>
+        <v>16.93</v>
       </c>
       <c r="D30" t="n">
-        <v>16758</v>
+        <v>23282</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>98.83</v>
+        <v>9.73</v>
       </c>
       <c r="B31" t="n">
-        <v>41987</v>
+        <v>31129</v>
       </c>
       <c r="C31" t="n">
-        <v>95.90000000000001</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="D31" t="n">
-        <v>23094</v>
+        <v>13525</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>106.44</v>
+        <v>10.69</v>
       </c>
       <c r="B32" t="n">
-        <v>42551</v>
+        <v>30896</v>
       </c>
       <c r="C32" t="n">
-        <v>106.07</v>
+        <v>13.5</v>
       </c>
       <c r="D32" t="n">
-        <v>26766</v>
+        <v>17656</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>93.15000000000001</v>
+        <v>10.8</v>
       </c>
       <c r="B33" t="n">
-        <v>29458</v>
+        <v>26625</v>
       </c>
       <c r="C33" t="n">
-        <v>94.3</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="D33" t="n">
-        <v>16198</v>
+        <v>26102</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>163.1</v>
+        <v>11.16</v>
       </c>
       <c r="B34" t="n">
-        <v>22925</v>
+        <v>31058</v>
       </c>
       <c r="C34" t="n">
-        <v>166.15</v>
+        <v>10.43</v>
       </c>
       <c r="D34" t="n">
-        <v>23285</v>
+        <v>11058</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>101.81</v>
+        <v>12.61</v>
       </c>
       <c r="B35" t="n">
-        <v>44289</v>
+        <v>29381</v>
       </c>
       <c r="C35" t="n">
-        <v>99.39</v>
+        <v>7.55</v>
       </c>
       <c r="D35" t="n">
-        <v>12637</v>
+        <v>13702</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>97.34999999999999</v>
+        <v>13.07</v>
       </c>
       <c r="B36" t="n">
-        <v>40672</v>
+        <v>30234</v>
       </c>
       <c r="C36" t="n">
-        <v>99.70999999999999</v>
+        <v>17.79</v>
       </c>
       <c r="D36" t="n">
-        <v>17622</v>
+        <v>25425</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>108.38</v>
+        <v>13.63</v>
       </c>
       <c r="B37" t="n">
-        <v>36495</v>
+        <v>27121</v>
       </c>
       <c r="C37" t="n">
-        <v>110.34</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="D37" t="n">
-        <v>10725</v>
+        <v>21660</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>95.53</v>
+        <v>13.79</v>
       </c>
       <c r="B38" t="n">
-        <v>33403</v>
+        <v>30081</v>
       </c>
       <c r="C38" t="n">
-        <v>98.97</v>
+        <v>6.85</v>
       </c>
       <c r="D38" t="n">
-        <v>16469</v>
+        <v>20899</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>91.87</v>
+        <v>13.87</v>
       </c>
       <c r="B39" t="n">
-        <v>24347</v>
+        <v>28821</v>
       </c>
       <c r="C39" t="n">
-        <v>90.56999999999999</v>
+        <v>12.64</v>
       </c>
       <c r="D39" t="n">
-        <v>20491</v>
+        <v>28809</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>100.37</v>
+        <v>15.34</v>
       </c>
       <c r="B40" t="n">
-        <v>45355</v>
+        <v>27563</v>
       </c>
       <c r="C40" t="n">
-        <v>101.55</v>
+        <v>19.08</v>
       </c>
       <c r="D40" t="n">
-        <v>25900</v>
+        <v>10033</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>110.15</v>
+        <v>15.64</v>
       </c>
       <c r="B41" t="n">
-        <v>30151</v>
+        <v>29125</v>
       </c>
       <c r="C41" t="n">
-        <v>110.22</v>
+        <v>12.43</v>
       </c>
       <c r="D41" t="n">
-        <v>22209</v>
+        <v>10278</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>103.52</v>
+        <v>16.24</v>
       </c>
       <c r="B42" t="n">
-        <v>48276</v>
+        <v>23548</v>
       </c>
       <c r="C42" t="n">
-        <v>99.84</v>
+        <v>15.13</v>
       </c>
       <c r="D42" t="n">
-        <v>28644</v>
+        <v>25238</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>106.57</v>
+        <v>16.47</v>
       </c>
       <c r="B43" t="n">
-        <v>42635</v>
+        <v>27365</v>
       </c>
       <c r="C43" t="n">
-        <v>103.33</v>
+        <v>8.25</v>
       </c>
       <c r="D43" t="n">
-        <v>24393</v>
+        <v>11369</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>98.75</v>
+        <v>17.05</v>
       </c>
       <c r="B44" t="n">
-        <v>42714</v>
+        <v>26416</v>
       </c>
       <c r="C44" t="n">
-        <v>100.72</v>
+        <v>18.34</v>
       </c>
       <c r="D44" t="n">
-        <v>15294</v>
+        <v>20054</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>92.52</v>
+        <v>17.2</v>
       </c>
       <c r="B45" t="n">
-        <v>26360</v>
+        <v>25534</v>
       </c>
       <c r="C45" t="n">
-        <v>90.89</v>
+        <v>24.07</v>
       </c>
       <c r="D45" t="n">
-        <v>11959</v>
+        <v>28133</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>106.29</v>
+        <v>17.33</v>
       </c>
       <c r="B46" t="n">
-        <v>44431</v>
+        <v>27114</v>
       </c>
       <c r="C46" t="n">
-        <v>109.73</v>
+        <v>24.07</v>
       </c>
       <c r="D46" t="n">
-        <v>24153</v>
+        <v>22583</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>112.04</v>
+        <v>17.49</v>
       </c>
       <c r="B47" t="n">
-        <v>25382</v>
+        <v>24841</v>
       </c>
       <c r="C47" t="n">
-        <v>111.06</v>
+        <v>20.01</v>
       </c>
       <c r="D47" t="n">
-        <v>17990</v>
+        <v>24712</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>111.35</v>
+        <v>17.8</v>
       </c>
       <c r="B48" t="n">
-        <v>31049</v>
+        <v>26168</v>
       </c>
       <c r="C48" t="n">
-        <v>115.57</v>
+        <v>12.98</v>
       </c>
       <c r="D48" t="n">
-        <v>15951</v>
+        <v>13227</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>104.45</v>
+        <v>17.86</v>
       </c>
       <c r="B49" t="n">
-        <v>45537</v>
+        <v>24099</v>
       </c>
       <c r="C49" t="n">
-        <v>105.75</v>
+        <v>19.85</v>
       </c>
       <c r="D49" t="n">
-        <v>24387</v>
+        <v>17513</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>107.44</v>
+        <v>18.22</v>
       </c>
       <c r="B50" t="n">
-        <v>40952</v>
+        <v>23974</v>
       </c>
       <c r="C50" t="n">
-        <v>105.48</v>
+        <v>24.66</v>
       </c>
       <c r="D50" t="n">
-        <v>15129</v>
+        <v>12303</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>115.26</v>
+        <v>18.71</v>
       </c>
       <c r="B51" t="n">
-        <v>23487</v>
+        <v>23900</v>
       </c>
       <c r="C51" t="n">
-        <v>119.27</v>
+        <v>11.37</v>
       </c>
       <c r="D51" t="n">
-        <v>18792</v>
+        <v>26771</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>97.14</v>
+        <v>18.84</v>
       </c>
       <c r="B52" t="n">
-        <v>39970</v>
+        <v>24189</v>
       </c>
       <c r="C52" t="n">
-        <v>96.79000000000001</v>
+        <v>5.95</v>
       </c>
       <c r="D52" t="n">
-        <v>17286</v>
+        <v>14084</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>0.74</v>
+        <v>20.48</v>
       </c>
       <c r="B53" t="n">
-        <v>21324</v>
+        <v>20961</v>
       </c>
       <c r="C53" t="n">
-        <v>1.36</v>
+        <v>18.74</v>
       </c>
       <c r="D53" t="n">
-        <v>29488</v>
+        <v>25588</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>107.83</v>
+        <v>20.83</v>
       </c>
       <c r="B54" t="n">
-        <v>37286</v>
+        <v>21278</v>
       </c>
       <c r="C54" t="n">
-        <v>106.47</v>
+        <v>15.44</v>
       </c>
       <c r="D54" t="n">
-        <v>23940</v>
+        <v>11433</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>77.56</v>
+        <v>20.96</v>
       </c>
       <c r="B55" t="n">
-        <v>21270</v>
+        <v>23139</v>
       </c>
       <c r="C55" t="n">
-        <v>75.7</v>
+        <v>24.76</v>
       </c>
       <c r="D55" t="n">
-        <v>11267</v>
+        <v>21884</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>105.52</v>
+        <v>21.67</v>
       </c>
       <c r="B56" t="n">
-        <v>46175</v>
+        <v>21937</v>
       </c>
       <c r="C56" t="n">
-        <v>105.92</v>
+        <v>23.79</v>
       </c>
       <c r="D56" t="n">
-        <v>16153</v>
+        <v>14767</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>101.63</v>
+        <v>21.73</v>
       </c>
       <c r="B57" t="n">
-        <v>47054</v>
+        <v>23444</v>
       </c>
       <c r="C57" t="n">
-        <v>104.76</v>
+        <v>22.43</v>
       </c>
       <c r="D57" t="n">
-        <v>13001</v>
+        <v>23783</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>96.53</v>
+        <v>22</v>
       </c>
       <c r="B58" t="n">
-        <v>36442</v>
+        <v>22041</v>
       </c>
       <c r="C58" t="n">
-        <v>98.51000000000001</v>
+        <v>23.91</v>
       </c>
       <c r="D58" t="n">
-        <v>17167</v>
+        <v>13842</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>109.17</v>
+        <v>22.67</v>
       </c>
       <c r="B59" t="n">
-        <v>31678</v>
+        <v>22624</v>
       </c>
       <c r="C59" t="n">
-        <v>109.09</v>
+        <v>23.05</v>
       </c>
       <c r="D59" t="n">
-        <v>17495</v>
+        <v>27021</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>111.92</v>
+        <v>22.82</v>
       </c>
       <c r="B60" t="n">
-        <v>27860</v>
+        <v>24982</v>
       </c>
       <c r="C60" t="n">
-        <v>115.65</v>
+        <v>27.08</v>
       </c>
       <c r="D60" t="n">
-        <v>10442</v>
+        <v>18038</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>100.56</v>
+        <v>22.85</v>
       </c>
       <c r="B61" t="n">
-        <v>46597</v>
+        <v>24746</v>
       </c>
       <c r="C61" t="n">
-        <v>103.95</v>
+        <v>12.37</v>
       </c>
       <c r="D61" t="n">
-        <v>10001</v>
+        <v>10445</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>101.02</v>
+        <v>24.43</v>
       </c>
       <c r="B62" t="n">
-        <v>44109</v>
+        <v>23848</v>
       </c>
       <c r="C62" t="n">
-        <v>98.11</v>
+        <v>25.19</v>
       </c>
       <c r="D62" t="n">
-        <v>10705</v>
+        <v>13300</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>97.42</v>
+        <v>24.6</v>
       </c>
       <c r="B63" t="n">
-        <v>39674</v>
+        <v>22779</v>
       </c>
       <c r="C63" t="n">
-        <v>98.89</v>
+        <v>32.51</v>
       </c>
       <c r="D63" t="n">
-        <v>26507</v>
+        <v>25993</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>107.23</v>
+        <v>24.74</v>
       </c>
       <c r="B64" t="n">
-        <v>38722</v>
+        <v>21709</v>
       </c>
       <c r="C64" t="n">
-        <v>104.54</v>
+        <v>31.17</v>
       </c>
       <c r="D64" t="n">
-        <v>23589</v>
+        <v>23297</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>95.04000000000001</v>
+        <v>25.41</v>
       </c>
       <c r="B65" t="n">
-        <v>33821</v>
+        <v>20229</v>
       </c>
       <c r="C65" t="n">
-        <v>91.13</v>
+        <v>21.69</v>
       </c>
       <c r="D65" t="n">
-        <v>21560</v>
+        <v>17857</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>114.59</v>
+        <v>25.64</v>
       </c>
       <c r="B66" t="n">
-        <v>22941</v>
+        <v>23541</v>
       </c>
       <c r="C66" t="n">
-        <v>117.07</v>
+        <v>35.49</v>
       </c>
       <c r="D66" t="n">
-        <v>20596</v>
+        <v>20560</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>94.77</v>
+        <v>26.13</v>
       </c>
       <c r="B67" t="n">
-        <v>32639</v>
+        <v>20565</v>
       </c>
       <c r="C67" t="n">
-        <v>91.73999999999999</v>
+        <v>24.3</v>
       </c>
       <c r="D67" t="n">
-        <v>29525</v>
+        <v>24356</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130.86</v>
+        <v>26.45</v>
       </c>
       <c r="B68" t="n">
-        <v>23079</v>
+        <v>19842</v>
       </c>
       <c r="C68" t="n">
-        <v>127.09</v>
+        <v>14.3</v>
       </c>
       <c r="D68" t="n">
-        <v>17437</v>
+        <v>18350</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>103.79</v>
+        <v>26.81</v>
       </c>
       <c r="B69" t="n">
-        <v>44683</v>
+        <v>20161</v>
       </c>
       <c r="C69" t="n">
-        <v>102.34</v>
+        <v>22.5</v>
       </c>
       <c r="D69" t="n">
-        <v>11047</v>
+        <v>22728</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>110.8</v>
+        <v>26.81</v>
       </c>
       <c r="B70" t="n">
-        <v>29917</v>
+        <v>21115</v>
       </c>
       <c r="C70" t="n">
-        <v>107.11</v>
+        <v>30.8</v>
       </c>
       <c r="D70" t="n">
-        <v>17044</v>
+        <v>20306</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>104.42</v>
+        <v>27.46</v>
       </c>
       <c r="B71" t="n">
-        <v>46475</v>
+        <v>19910</v>
       </c>
       <c r="C71" t="n">
-        <v>104.89</v>
+        <v>29.2</v>
       </c>
       <c r="D71" t="n">
-        <v>26822</v>
+        <v>28449</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>95.34999999999999</v>
+        <v>27.63</v>
       </c>
       <c r="B72" t="n">
-        <v>35630</v>
+        <v>21892</v>
       </c>
       <c r="C72" t="n">
-        <v>94.58</v>
+        <v>20.44</v>
       </c>
       <c r="D72" t="n">
-        <v>28784</v>
+        <v>25001</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>111.64</v>
+        <v>27.73</v>
       </c>
       <c r="B73" t="n">
-        <v>27721</v>
+        <v>23807</v>
       </c>
       <c r="C73" t="n">
-        <v>112.37</v>
+        <v>29.1</v>
       </c>
       <c r="D73" t="n">
-        <v>17312</v>
+        <v>20749</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>94.05</v>
+        <v>28.11</v>
       </c>
       <c r="B74" t="n">
-        <v>33265</v>
+        <v>20617</v>
       </c>
       <c r="C74" t="n">
-        <v>92.13</v>
+        <v>25.68</v>
       </c>
       <c r="D74" t="n">
-        <v>27711</v>
+        <v>13892</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>92.12</v>
+        <v>28.24</v>
       </c>
       <c r="B75" t="n">
-        <v>27825</v>
+        <v>20477</v>
       </c>
       <c r="C75" t="n">
-        <v>93.84</v>
+        <v>22.58</v>
       </c>
       <c r="D75" t="n">
-        <v>17025</v>
+        <v>26701</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>113.28</v>
+        <v>28.62</v>
       </c>
       <c r="B76" t="n">
-        <v>25538</v>
+        <v>18714</v>
       </c>
       <c r="C76" t="n">
-        <v>110.09</v>
+        <v>24.01</v>
       </c>
       <c r="D76" t="n">
-        <v>24640</v>
+        <v>15840</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>95.47</v>
+        <v>28.93</v>
       </c>
       <c r="B77" t="n">
-        <v>35170</v>
+        <v>21666</v>
       </c>
       <c r="C77" t="n">
-        <v>96.58</v>
+        <v>23.17</v>
       </c>
       <c r="D77" t="n">
-        <v>26918</v>
+        <v>11165</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>107.77</v>
+        <v>28.97</v>
       </c>
       <c r="B78" t="n">
-        <v>37913</v>
+        <v>24727</v>
       </c>
       <c r="C78" t="n">
-        <v>109.26</v>
+        <v>32.11</v>
       </c>
       <c r="D78" t="n">
-        <v>28975</v>
+        <v>20387</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>97.58</v>
+        <v>29.17</v>
       </c>
       <c r="B79" t="n">
-        <v>40341</v>
+        <v>20801</v>
       </c>
       <c r="C79" t="n">
-        <v>97.81</v>
+        <v>36.5</v>
       </c>
       <c r="D79" t="n">
-        <v>19484</v>
+        <v>26507</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>91.90000000000001</v>
+        <v>29.18</v>
       </c>
       <c r="B80" t="n">
-        <v>23652</v>
+        <v>20834</v>
       </c>
       <c r="C80" t="n">
-        <v>88.84999999999999</v>
+        <v>20.25</v>
       </c>
       <c r="D80" t="n">
-        <v>12413</v>
+        <v>13170</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>100.42</v>
+        <v>29.77</v>
       </c>
       <c r="B81" t="n">
-        <v>43822</v>
+        <v>22285</v>
       </c>
       <c r="C81" t="n">
-        <v>102.47</v>
+        <v>21.89</v>
       </c>
       <c r="D81" t="n">
-        <v>22059</v>
+        <v>16922</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>105.75</v>
+        <v>29.8</v>
       </c>
       <c r="B82" t="n">
-        <v>45839</v>
+        <v>20258</v>
       </c>
       <c r="C82" t="n">
-        <v>102.38</v>
+        <v>19.95</v>
       </c>
       <c r="D82" t="n">
-        <v>27561</v>
+        <v>12332</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>101.63</v>
+        <v>29.83</v>
       </c>
       <c r="B83" t="n">
-        <v>45619</v>
+        <v>21898</v>
       </c>
       <c r="C83" t="n">
-        <v>102.39</v>
+        <v>31.51</v>
       </c>
       <c r="D83" t="n">
-        <v>18578</v>
+        <v>22668</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>52.62</v>
+        <v>29.98</v>
       </c>
       <c r="B84" t="n">
-        <v>23958</v>
+        <v>21526</v>
       </c>
       <c r="C84" t="n">
-        <v>50.81</v>
+        <v>35.48</v>
       </c>
       <c r="D84" t="n">
-        <v>16704</v>
+        <v>25558</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>109.92</v>
+        <v>30.12</v>
       </c>
       <c r="B85" t="n">
-        <v>31280</v>
+        <v>18776</v>
       </c>
       <c r="C85" t="n">
-        <v>107.88</v>
+        <v>35.62</v>
       </c>
       <c r="D85" t="n">
-        <v>14304</v>
+        <v>11031</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>100.49</v>
+        <v>30.15</v>
       </c>
       <c r="B86" t="n">
-        <v>43842</v>
+        <v>19411</v>
       </c>
       <c r="C86" t="n">
-        <v>101.79</v>
+        <v>25.75</v>
       </c>
       <c r="D86" t="n">
-        <v>10182</v>
+        <v>15989</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>99.53</v>
+        <v>30.22</v>
       </c>
       <c r="B87" t="n">
-        <v>44241</v>
+        <v>20972</v>
       </c>
       <c r="C87" t="n">
-        <v>96.95</v>
+        <v>29.83</v>
       </c>
       <c r="D87" t="n">
-        <v>23731</v>
+        <v>17636</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>113.03</v>
+        <v>30.34</v>
       </c>
       <c r="B88" t="n">
-        <v>24788</v>
+        <v>22279</v>
       </c>
       <c r="C88" t="n">
-        <v>116.1</v>
+        <v>26.4</v>
       </c>
       <c r="D88" t="n">
-        <v>13287</v>
+        <v>24840</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>98.16</v>
+        <v>30.98</v>
       </c>
       <c r="B89" t="n">
-        <v>42576</v>
+        <v>24145</v>
       </c>
       <c r="C89" t="n">
-        <v>98.45</v>
+        <v>31.9</v>
       </c>
       <c r="D89" t="n">
-        <v>13394</v>
+        <v>10733</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>110.68</v>
+        <v>31.14</v>
       </c>
       <c r="B90" t="n">
-        <v>32153</v>
+        <v>23428</v>
       </c>
       <c r="C90" t="n">
-        <v>113.76</v>
+        <v>32.7</v>
       </c>
       <c r="D90" t="n">
-        <v>13923</v>
+        <v>29147</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>109.49</v>
+        <v>31.32</v>
       </c>
       <c r="B91" t="n">
-        <v>34310</v>
+        <v>22915</v>
       </c>
       <c r="C91" t="n">
-        <v>112.58</v>
+        <v>25.19</v>
       </c>
       <c r="D91" t="n">
-        <v>11135</v>
+        <v>28607</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>105.23</v>
+        <v>31.33</v>
       </c>
       <c r="B92" t="n">
-        <v>46996</v>
+        <v>21265</v>
       </c>
       <c r="C92" t="n">
-        <v>107.04</v>
+        <v>24.83</v>
       </c>
       <c r="D92" t="n">
-        <v>26966</v>
+        <v>19591</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>109.17</v>
+        <v>31.35</v>
       </c>
       <c r="B93" t="n">
-        <v>36020</v>
+        <v>20241</v>
       </c>
       <c r="C93" t="n">
-        <v>111.87</v>
+        <v>29.61</v>
       </c>
       <c r="D93" t="n">
-        <v>14566</v>
+        <v>29512</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>12.71</v>
+        <v>31.39</v>
       </c>
       <c r="B94" t="n">
-        <v>25255</v>
+        <v>24248</v>
       </c>
       <c r="C94" t="n">
-        <v>12.67</v>
+        <v>28.1</v>
       </c>
       <c r="D94" t="n">
-        <v>11442</v>
+        <v>13456</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>103.78</v>
+        <v>31.43</v>
       </c>
       <c r="B95" t="n">
-        <v>48047</v>
+        <v>23603</v>
       </c>
       <c r="C95" t="n">
-        <v>107.63</v>
+        <v>29.39</v>
       </c>
       <c r="D95" t="n">
-        <v>25353</v>
+        <v>27994</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>111.6</v>
+        <v>32.58</v>
       </c>
       <c r="B96" t="n">
-        <v>27162</v>
+        <v>22109</v>
       </c>
       <c r="C96" t="n">
-        <v>114.29</v>
+        <v>26.72</v>
       </c>
       <c r="D96" t="n">
-        <v>11866</v>
+        <v>12739</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>94.31</v>
+        <v>32.69</v>
       </c>
       <c r="B97" t="n">
-        <v>32607</v>
+        <v>22749</v>
       </c>
       <c r="C97" t="n">
-        <v>95.13</v>
+        <v>34.07</v>
       </c>
       <c r="D97" t="n">
-        <v>22411</v>
+        <v>26838</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>93.79000000000001</v>
+        <v>32.71</v>
       </c>
       <c r="B98" t="n">
-        <v>27789</v>
+        <v>21764</v>
       </c>
       <c r="C98" t="n">
-        <v>97.19</v>
+        <v>34.27</v>
       </c>
       <c r="D98" t="n">
-        <v>12770</v>
+        <v>29079</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>104.04</v>
+        <v>32.89</v>
       </c>
       <c r="B99" t="n">
-        <v>47699</v>
+        <v>20980</v>
       </c>
       <c r="C99" t="n">
-        <v>104.35</v>
+        <v>37.76</v>
       </c>
       <c r="D99" t="n">
-        <v>12573</v>
+        <v>21864</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>97.98999999999999</v>
+        <v>32.99</v>
       </c>
       <c r="B100" t="n">
-        <v>42187</v>
+        <v>22105</v>
       </c>
       <c r="C100" t="n">
-        <v>98.31</v>
+        <v>27.75</v>
       </c>
       <c r="D100" t="n">
-        <v>26457</v>
+        <v>13340</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>103.46</v>
+        <v>32.99</v>
       </c>
       <c r="B101" t="n">
-        <v>45408</v>
+        <v>19326</v>
       </c>
       <c r="C101" t="n">
-        <v>105</v>
+        <v>27.78</v>
       </c>
       <c r="D101" t="n">
-        <v>26191</v>
+        <v>18142</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>154.21</v>
+        <v>33.1</v>
       </c>
       <c r="B102" t="n">
-        <v>23795</v>
+        <v>20221</v>
       </c>
       <c r="C102" t="n">
-        <v>156.29</v>
+        <v>39.75</v>
       </c>
       <c r="D102" t="n">
-        <v>14358</v>
+        <v>14526</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>102.77</v>
+        <v>33.89</v>
       </c>
       <c r="B103" t="n">
-        <v>45611</v>
+        <v>23232</v>
       </c>
       <c r="C103" t="n">
-        <v>103.89</v>
+        <v>31.48</v>
       </c>
       <c r="D103" t="n">
-        <v>25557</v>
+        <v>10197</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>111.54</v>
+        <v>34.44</v>
       </c>
       <c r="B104" t="n">
-        <v>27134</v>
+        <v>21705</v>
       </c>
       <c r="C104" t="n">
-        <v>108.88</v>
+        <v>40.46</v>
       </c>
       <c r="D104" t="n">
-        <v>24423</v>
+        <v>28455</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>112.36</v>
+        <v>34.72</v>
       </c>
       <c r="B105" t="n">
-        <v>26376</v>
+        <v>19994</v>
       </c>
       <c r="C105" t="n">
-        <v>109.43</v>
+        <v>31.09</v>
       </c>
       <c r="D105" t="n">
-        <v>22589</v>
+        <v>13982</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>100.3</v>
+        <v>35.02</v>
       </c>
       <c r="B106" t="n">
-        <v>44684</v>
+        <v>21825</v>
       </c>
       <c r="C106" t="n">
-        <v>98.40000000000001</v>
+        <v>25.44</v>
       </c>
       <c r="D106" t="n">
-        <v>27504</v>
+        <v>21053</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>103.69</v>
+        <v>35.08</v>
       </c>
       <c r="B107" t="n">
-        <v>46311</v>
+        <v>19124</v>
       </c>
       <c r="C107" t="n">
-        <v>104.3</v>
+        <v>33.81</v>
       </c>
       <c r="D107" t="n">
-        <v>13558</v>
+        <v>24451</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>136.84</v>
+        <v>35.75</v>
       </c>
       <c r="B108" t="n">
-        <v>19125</v>
+        <v>23270</v>
       </c>
       <c r="C108" t="n">
-        <v>131.4</v>
+        <v>32.76</v>
       </c>
       <c r="D108" t="n">
-        <v>20278</v>
+        <v>10218</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>101.77</v>
+        <v>35.87</v>
       </c>
       <c r="B109" t="n">
-        <v>46981</v>
+        <v>21134</v>
       </c>
       <c r="C109" t="n">
-        <v>99.62</v>
+        <v>27.82</v>
       </c>
       <c r="D109" t="n">
-        <v>27218</v>
+        <v>14642</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>105.41</v>
+        <v>36.03</v>
       </c>
       <c r="B110" t="n">
-        <v>44380</v>
+        <v>20627</v>
       </c>
       <c r="C110" t="n">
-        <v>102.79</v>
+        <v>41.96</v>
       </c>
       <c r="D110" t="n">
-        <v>28470</v>
+        <v>19942</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>109.78</v>
+        <v>36.33</v>
       </c>
       <c r="B111" t="n">
-        <v>32613</v>
+        <v>21788</v>
       </c>
       <c r="C111" t="n">
-        <v>108.73</v>
+        <v>31.65</v>
       </c>
       <c r="D111" t="n">
-        <v>23483</v>
+        <v>27055</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>139.71</v>
+        <v>36.64</v>
       </c>
       <c r="B112" t="n">
-        <v>25198</v>
+        <v>21270</v>
       </c>
       <c r="C112" t="n">
-        <v>140.48</v>
+        <v>47.55</v>
       </c>
       <c r="D112" t="n">
-        <v>23673</v>
+        <v>13602</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>48.65</v>
+        <v>36.76</v>
       </c>
       <c r="B113" t="n">
-        <v>21738</v>
+        <v>24854</v>
       </c>
       <c r="C113" t="n">
-        <v>46.96</v>
+        <v>43.74</v>
       </c>
       <c r="D113" t="n">
-        <v>17844</v>
+        <v>10339</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>144.81</v>
+        <v>36.86</v>
       </c>
       <c r="B114" t="n">
-        <v>22636</v>
+        <v>21988</v>
       </c>
       <c r="C114" t="n">
-        <v>146.75</v>
+        <v>25.63</v>
       </c>
       <c r="D114" t="n">
-        <v>19992</v>
+        <v>16177</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>58.67</v>
+        <v>36.9</v>
       </c>
       <c r="B115" t="n">
-        <v>23169</v>
+        <v>19650</v>
       </c>
       <c r="C115" t="n">
-        <v>56.89</v>
+        <v>29.4</v>
       </c>
       <c r="D115" t="n">
-        <v>20709</v>
+        <v>11434</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>90.29000000000001</v>
+        <v>37.29</v>
       </c>
       <c r="B116" t="n">
-        <v>21686</v>
+        <v>19982</v>
       </c>
       <c r="C116" t="n">
-        <v>87.48999999999999</v>
+        <v>33.38</v>
       </c>
       <c r="D116" t="n">
-        <v>11821</v>
+        <v>14492</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>107.2</v>
+        <v>37.43</v>
       </c>
       <c r="B117" t="n">
-        <v>38124</v>
+        <v>21038</v>
       </c>
       <c r="C117" t="n">
-        <v>103.85</v>
+        <v>38</v>
       </c>
       <c r="D117" t="n">
-        <v>17056</v>
+        <v>15162</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>138.69</v>
+        <v>37.95</v>
       </c>
       <c r="B118" t="n">
-        <v>21511</v>
+        <v>19428</v>
       </c>
       <c r="C118" t="n">
-        <v>136.74</v>
+        <v>31.7</v>
       </c>
       <c r="D118" t="n">
-        <v>13888</v>
+        <v>21617</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>32.76</v>
+        <v>38.44</v>
       </c>
       <c r="B119" t="n">
-        <v>23897</v>
+        <v>22746</v>
       </c>
       <c r="C119" t="n">
-        <v>31.6</v>
+        <v>40.32</v>
       </c>
       <c r="D119" t="n">
-        <v>19041</v>
+        <v>24531</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>33.98</v>
+        <v>38.85</v>
       </c>
       <c r="B120" t="n">
-        <v>23014</v>
+        <v>20839</v>
       </c>
       <c r="C120" t="n">
-        <v>32.17</v>
+        <v>63.52</v>
       </c>
       <c r="D120" t="n">
-        <v>12785</v>
+        <v>16304</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>113.29</v>
+        <v>39.14</v>
       </c>
       <c r="B121" t="n">
-        <v>24999</v>
+        <v>21716</v>
       </c>
       <c r="C121" t="n">
-        <v>112.92</v>
+        <v>44.31</v>
       </c>
       <c r="D121" t="n">
-        <v>13907</v>
+        <v>23589</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>105.46</v>
+        <v>39.21</v>
       </c>
       <c r="B122" t="n">
-        <v>45354</v>
+        <v>20531</v>
       </c>
       <c r="C122" t="n">
-        <v>104.57</v>
+        <v>50.12</v>
       </c>
       <c r="D122" t="n">
-        <v>21903</v>
+        <v>20568</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>92.98</v>
+        <v>39.77</v>
       </c>
       <c r="B123" t="n">
-        <v>27668</v>
+        <v>21991</v>
       </c>
       <c r="C123" t="n">
-        <v>94.97</v>
+        <v>43.02</v>
       </c>
       <c r="D123" t="n">
-        <v>24953</v>
+        <v>11684</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>109.34</v>
+        <v>39.87</v>
       </c>
       <c r="B124" t="n">
-        <v>34449</v>
+        <v>20291</v>
       </c>
       <c r="C124" t="n">
-        <v>113.24</v>
+        <v>52.56</v>
       </c>
       <c r="D124" t="n">
-        <v>16087</v>
+        <v>20975</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>98.14</v>
+        <v>40.27</v>
       </c>
       <c r="B125" t="n">
-        <v>39650</v>
+        <v>23274</v>
       </c>
       <c r="C125" t="n">
-        <v>97.75</v>
+        <v>44.38</v>
       </c>
       <c r="D125" t="n">
-        <v>17685</v>
+        <v>23854</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>101.01</v>
+        <v>40.65</v>
       </c>
       <c r="B126" t="n">
-        <v>45648</v>
+        <v>18707</v>
       </c>
       <c r="C126" t="n">
-        <v>104.39</v>
+        <v>42.56</v>
       </c>
       <c r="D126" t="n">
-        <v>25647</v>
+        <v>18458</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>97.97</v>
+        <v>41.03</v>
       </c>
       <c r="B127" t="n">
-        <v>39206</v>
+        <v>22097</v>
       </c>
       <c r="C127" t="n">
-        <v>98.88</v>
+        <v>32.35</v>
       </c>
       <c r="D127" t="n">
-        <v>11869</v>
+        <v>27759</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>111.93</v>
+        <v>41.67</v>
       </c>
       <c r="B128" t="n">
-        <v>28299</v>
+        <v>21031</v>
       </c>
       <c r="C128" t="n">
-        <v>107.87</v>
+        <v>47.3</v>
       </c>
       <c r="D128" t="n">
-        <v>13453</v>
+        <v>27323</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>110.64</v>
+        <v>41.68</v>
       </c>
       <c r="B129" t="n">
-        <v>26884</v>
+        <v>20562</v>
       </c>
       <c r="C129" t="n">
-        <v>107.64</v>
+        <v>43.61</v>
       </c>
       <c r="D129" t="n">
-        <v>21345</v>
+        <v>16588</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>91.11</v>
+        <v>42.05</v>
       </c>
       <c r="B130" t="n">
-        <v>26441</v>
+        <v>22193</v>
       </c>
       <c r="C130" t="n">
-        <v>90.88</v>
+        <v>52.79</v>
       </c>
       <c r="D130" t="n">
-        <v>19664</v>
+        <v>28459</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>97.23</v>
+        <v>42.46</v>
       </c>
       <c r="B131" t="n">
-        <v>40084</v>
+        <v>19834</v>
       </c>
       <c r="C131" t="n">
-        <v>99.63</v>
+        <v>53.31</v>
       </c>
       <c r="D131" t="n">
-        <v>15154</v>
+        <v>24093</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>102.59</v>
+        <v>42.74</v>
       </c>
       <c r="B132" t="n">
-        <v>46241</v>
+        <v>21427</v>
       </c>
       <c r="C132" t="n">
-        <v>101.23</v>
+        <v>37.01</v>
       </c>
       <c r="D132" t="n">
-        <v>26095</v>
+        <v>22516</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>114.17</v>
+        <v>42.89</v>
       </c>
       <c r="B133" t="n">
-        <v>23558</v>
+        <v>19816</v>
       </c>
       <c r="C133" t="n">
-        <v>115.44</v>
+        <v>41.06</v>
       </c>
       <c r="D133" t="n">
-        <v>12531</v>
+        <v>25179</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>91.56999999999999</v>
+        <v>43.04</v>
       </c>
       <c r="B134" t="n">
-        <v>24145</v>
+        <v>21406</v>
       </c>
       <c r="C134" t="n">
-        <v>88.69</v>
+        <v>50.85</v>
       </c>
       <c r="D134" t="n">
-        <v>26638</v>
+        <v>28178</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>109.46</v>
+        <v>43.15</v>
       </c>
       <c r="B135" t="n">
-        <v>34506</v>
+        <v>22524</v>
       </c>
       <c r="C135" t="n">
-        <v>109.6</v>
+        <v>43.94</v>
       </c>
       <c r="D135" t="n">
-        <v>27782</v>
+        <v>11802</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>113.93</v>
+        <v>43.51</v>
       </c>
       <c r="B136" t="n">
-        <v>23895</v>
+        <v>22013</v>
       </c>
       <c r="C136" t="n">
-        <v>110.24</v>
+        <v>50.11</v>
       </c>
       <c r="D136" t="n">
-        <v>10840</v>
+        <v>20625</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>104.17</v>
+        <v>44.12</v>
       </c>
       <c r="B137" t="n">
-        <v>48785</v>
+        <v>21287</v>
       </c>
       <c r="C137" t="n">
-        <v>108.04</v>
+        <v>40.82</v>
       </c>
       <c r="D137" t="n">
-        <v>19567</v>
+        <v>28496</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>108.64</v>
+        <v>44.62</v>
       </c>
       <c r="B138" t="n">
-        <v>37677</v>
+        <v>22272</v>
       </c>
       <c r="C138" t="n">
-        <v>109.14</v>
+        <v>43.41</v>
       </c>
       <c r="D138" t="n">
-        <v>29627</v>
+        <v>26485</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>109.81</v>
+        <v>46.31</v>
       </c>
       <c r="B139" t="n">
-        <v>32462</v>
+        <v>20154</v>
       </c>
       <c r="C139" t="n">
-        <v>107.91</v>
+        <v>37.37</v>
       </c>
       <c r="D139" t="n">
-        <v>29492</v>
+        <v>10465</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>105.75</v>
+        <v>46.46</v>
       </c>
       <c r="B140" t="n">
-        <v>44735</v>
+        <v>21730</v>
       </c>
       <c r="C140" t="n">
-        <v>105.73</v>
+        <v>42.61</v>
       </c>
       <c r="D140" t="n">
-        <v>16050</v>
+        <v>12548</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>39.96</v>
+        <v>46.88</v>
       </c>
       <c r="B141" t="n">
-        <v>24378</v>
+        <v>21832</v>
       </c>
       <c r="C141" t="n">
-        <v>38.29</v>
+        <v>44.15</v>
       </c>
       <c r="D141" t="n">
-        <v>15333</v>
+        <v>10899</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>97.86</v>
+        <v>46.9</v>
       </c>
       <c r="B142" t="n">
-        <v>37268</v>
+        <v>22708</v>
       </c>
       <c r="C142" t="n">
-        <v>100.76</v>
+        <v>56.65</v>
       </c>
       <c r="D142" t="n">
-        <v>10325</v>
+        <v>21853</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>92.06999999999999</v>
+        <v>46.98</v>
       </c>
       <c r="B143" t="n">
-        <v>28099</v>
+        <v>18413</v>
       </c>
       <c r="C143" t="n">
-        <v>89.87</v>
+        <v>40.05</v>
       </c>
       <c r="D143" t="n">
-        <v>23404</v>
+        <v>27499</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>90.12</v>
+        <v>47.59</v>
       </c>
       <c r="B144" t="n">
-        <v>23866</v>
+        <v>20778</v>
       </c>
       <c r="C144" t="n">
-        <v>89</v>
+        <v>56.18</v>
       </c>
       <c r="D144" t="n">
-        <v>18973</v>
+        <v>11980</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>106.53</v>
+        <v>47.83</v>
       </c>
       <c r="B145" t="n">
-        <v>44021</v>
+        <v>21674</v>
       </c>
       <c r="C145" t="n">
-        <v>105.64</v>
+        <v>52.19</v>
       </c>
       <c r="D145" t="n">
-        <v>27308</v>
+        <v>15685</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>94.73</v>
+        <v>48.02</v>
       </c>
       <c r="B146" t="n">
-        <v>34377</v>
+        <v>20768</v>
       </c>
       <c r="C146" t="n">
-        <v>97.70999999999999</v>
+        <v>47.45</v>
       </c>
       <c r="D146" t="n">
-        <v>24808</v>
+        <v>19882</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>91.2</v>
+        <v>48.07</v>
       </c>
       <c r="B147" t="n">
-        <v>24985</v>
+        <v>20884</v>
       </c>
       <c r="C147" t="n">
-        <v>93.17</v>
+        <v>56.36</v>
       </c>
       <c r="D147" t="n">
-        <v>15411</v>
+        <v>26887</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>92.52</v>
+        <v>48.54</v>
       </c>
       <c r="B148" t="n">
-        <v>28611</v>
+        <v>19429</v>
       </c>
       <c r="C148" t="n">
-        <v>90.59999999999999</v>
+        <v>39.38</v>
       </c>
       <c r="D148" t="n">
-        <v>27740</v>
+        <v>25696</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>94.65000000000001</v>
+        <v>49.23</v>
       </c>
       <c r="B149" t="n">
-        <v>31473</v>
+        <v>19833</v>
       </c>
       <c r="C149" t="n">
-        <v>93.59</v>
+        <v>34.82</v>
       </c>
       <c r="D149" t="n">
-        <v>25454</v>
+        <v>10407</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>102.42</v>
+        <v>50.02</v>
       </c>
       <c r="B150" t="n">
-        <v>47411</v>
+        <v>20550</v>
       </c>
       <c r="C150" t="n">
-        <v>102.38</v>
+        <v>40.37</v>
       </c>
       <c r="D150" t="n">
-        <v>21115</v>
+        <v>25251</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>97.43000000000001</v>
+        <v>50.89</v>
       </c>
       <c r="B151" t="n">
-        <v>39981</v>
+        <v>19590</v>
       </c>
       <c r="C151" t="n">
-        <v>95.27</v>
+        <v>43.59</v>
       </c>
       <c r="D151" t="n">
-        <v>16562</v>
+        <v>16444</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>104.36</v>
+        <v>51.3</v>
       </c>
       <c r="B152" t="n">
-        <v>47309</v>
+        <v>20625</v>
       </c>
       <c r="C152" t="n">
-        <v>106.47</v>
+        <v>49.77</v>
       </c>
       <c r="D152" t="n">
-        <v>18837</v>
+        <v>18382</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>84.37</v>
+        <v>52.02</v>
       </c>
       <c r="B153" t="n">
-        <v>22226</v>
+        <v>20494</v>
       </c>
       <c r="C153" t="n">
-        <v>83.34</v>
+        <v>55.48</v>
       </c>
       <c r="D153" t="n">
-        <v>13382</v>
+        <v>14031</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>104.24</v>
+        <v>52.64</v>
       </c>
       <c r="B154" t="n">
-        <v>47796</v>
+        <v>21160</v>
       </c>
       <c r="C154" t="n">
-        <v>100.7</v>
+        <v>60.2</v>
       </c>
       <c r="D154" t="n">
-        <v>22222</v>
+        <v>19109</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>142.91</v>
+        <v>52.98</v>
       </c>
       <c r="B155" t="n">
-        <v>25360</v>
+        <v>22081</v>
       </c>
       <c r="C155" t="n">
-        <v>143.3</v>
+        <v>42.43</v>
       </c>
       <c r="D155" t="n">
-        <v>16575</v>
+        <v>24540</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>94.67</v>
+        <v>53.29</v>
       </c>
       <c r="B156" t="n">
-        <v>31657</v>
+        <v>20232</v>
       </c>
       <c r="C156" t="n">
-        <v>97.03</v>
+        <v>53</v>
       </c>
       <c r="D156" t="n">
-        <v>15857</v>
+        <v>24445</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>100.81</v>
+        <v>53.61</v>
       </c>
       <c r="B157" t="n">
-        <v>47189</v>
+        <v>19926</v>
       </c>
       <c r="C157" t="n">
-        <v>97.13</v>
+        <v>53.13</v>
       </c>
       <c r="D157" t="n">
-        <v>21790</v>
+        <v>15606</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>98.3</v>
+        <v>53.87</v>
       </c>
       <c r="B158" t="n">
-        <v>41020</v>
+        <v>20709</v>
       </c>
       <c r="C158" t="n">
-        <v>99.59</v>
+        <v>49.53</v>
       </c>
       <c r="D158" t="n">
-        <v>20055</v>
+        <v>22738</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>90.29000000000001</v>
+        <v>54.46</v>
       </c>
       <c r="B159" t="n">
-        <v>23404</v>
+        <v>20615</v>
       </c>
       <c r="C159" t="n">
-        <v>89.36</v>
+        <v>52.27</v>
       </c>
       <c r="D159" t="n">
-        <v>17453</v>
+        <v>19237</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>94.78</v>
+        <v>54.59</v>
       </c>
       <c r="B160" t="n">
-        <v>31915</v>
+        <v>19943</v>
       </c>
       <c r="C160" t="n">
-        <v>95.13</v>
+        <v>51</v>
       </c>
       <c r="D160" t="n">
-        <v>18822</v>
+        <v>22907</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>59.54</v>
+        <v>54.74</v>
       </c>
       <c r="B161" t="n">
-        <v>23091</v>
+        <v>19734</v>
       </c>
       <c r="C161" t="n">
-        <v>60.77</v>
+        <v>46.19</v>
       </c>
       <c r="D161" t="n">
-        <v>24597</v>
+        <v>15081</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>102.32</v>
+        <v>54.75</v>
       </c>
       <c r="B162" t="n">
-        <v>48789</v>
+        <v>20165</v>
       </c>
       <c r="C162" t="n">
-        <v>104.97</v>
+        <v>46.8</v>
       </c>
       <c r="D162" t="n">
-        <v>14749</v>
+        <v>24838</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>91.72</v>
+        <v>54.84</v>
       </c>
       <c r="B163" t="n">
-        <v>25625</v>
+        <v>20755</v>
       </c>
       <c r="C163" t="n">
-        <v>92.11</v>
+        <v>55.83</v>
       </c>
       <c r="D163" t="n">
-        <v>18549</v>
+        <v>14010</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>124.16</v>
+        <v>55.44</v>
       </c>
       <c r="B164" t="n">
-        <v>22033</v>
+        <v>21298</v>
       </c>
       <c r="C164" t="n">
-        <v>129.44</v>
+        <v>38.17</v>
       </c>
       <c r="D164" t="n">
-        <v>20936</v>
+        <v>15695</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>38.61</v>
+        <v>55.51</v>
       </c>
       <c r="B165" t="n">
-        <v>24918</v>
+        <v>20433</v>
       </c>
       <c r="C165" t="n">
-        <v>38.08</v>
+        <v>52.18</v>
       </c>
       <c r="D165" t="n">
-        <v>16471</v>
+        <v>15276</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>113.06</v>
+        <v>55.83</v>
       </c>
       <c r="B166" t="n">
-        <v>26939</v>
+        <v>22778</v>
       </c>
       <c r="C166" t="n">
-        <v>109.65</v>
+        <v>49.66</v>
       </c>
       <c r="D166" t="n">
-        <v>25422</v>
+        <v>28077</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>97.41</v>
+        <v>55.93</v>
       </c>
       <c r="B167" t="n">
-        <v>38337</v>
+        <v>19778</v>
       </c>
       <c r="C167" t="n">
-        <v>96.09999999999999</v>
+        <v>43.47</v>
       </c>
       <c r="D167" t="n">
-        <v>16878</v>
+        <v>19713</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>100.2</v>
+        <v>56.23</v>
       </c>
       <c r="B168" t="n">
-        <v>44784</v>
+        <v>22601</v>
       </c>
       <c r="C168" t="n">
-        <v>103.39</v>
+        <v>50.34</v>
       </c>
       <c r="D168" t="n">
-        <v>25067</v>
+        <v>18393</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>109.31</v>
+        <v>56.26</v>
       </c>
       <c r="B169" t="n">
-        <v>35582</v>
+        <v>19957</v>
       </c>
       <c r="C169" t="n">
-        <v>107.06</v>
+        <v>67.47</v>
       </c>
       <c r="D169" t="n">
-        <v>27559</v>
+        <v>20276</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>114.12</v>
+        <v>56.58</v>
       </c>
       <c r="B170" t="n">
-        <v>23764</v>
+        <v>20765</v>
       </c>
       <c r="C170" t="n">
-        <v>114.36</v>
+        <v>55.91</v>
       </c>
       <c r="D170" t="n">
-        <v>23913</v>
+        <v>29232</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>90.26000000000001</v>
+        <v>56.79</v>
       </c>
       <c r="B171" t="n">
-        <v>22069</v>
+        <v>20180</v>
       </c>
       <c r="C171" t="n">
-        <v>89.88</v>
+        <v>68.15000000000001</v>
       </c>
       <c r="D171" t="n">
-        <v>14210</v>
+        <v>25188</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>112.85</v>
+        <v>57.25</v>
       </c>
       <c r="B172" t="n">
-        <v>25578</v>
+        <v>18491</v>
       </c>
       <c r="C172" t="n">
-        <v>110.97</v>
+        <v>60.97</v>
       </c>
       <c r="D172" t="n">
-        <v>10003</v>
+        <v>26819</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>121.69</v>
+        <v>57.36</v>
       </c>
       <c r="B173" t="n">
-        <v>24327</v>
+        <v>20745</v>
       </c>
       <c r="C173" t="n">
-        <v>124.05</v>
+        <v>62.96</v>
       </c>
       <c r="D173" t="n">
-        <v>13656</v>
+        <v>21595</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>100.75</v>
+        <v>57.56</v>
       </c>
       <c r="B174" t="n">
-        <v>47388</v>
+        <v>19427</v>
       </c>
       <c r="C174" t="n">
-        <v>102.68</v>
+        <v>52.85</v>
       </c>
       <c r="D174" t="n">
-        <v>13742</v>
+        <v>29718</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>104.87</v>
+        <v>57.63</v>
       </c>
       <c r="B175" t="n">
-        <v>43772</v>
+        <v>20500</v>
       </c>
       <c r="C175" t="n">
-        <v>104.95</v>
+        <v>64.06999999999999</v>
       </c>
       <c r="D175" t="n">
-        <v>20365</v>
+        <v>25850</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>95.03</v>
+        <v>57.73</v>
       </c>
       <c r="B176" t="n">
-        <v>31930</v>
+        <v>19492</v>
       </c>
       <c r="C176" t="n">
-        <v>92.2</v>
+        <v>51.11</v>
       </c>
       <c r="D176" t="n">
-        <v>28641</v>
+        <v>25097</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>98.77</v>
+        <v>57.84</v>
       </c>
       <c r="B177" t="n">
-        <v>43475</v>
+        <v>21535</v>
       </c>
       <c r="C177" t="n">
-        <v>100.67</v>
+        <v>65.12</v>
       </c>
       <c r="D177" t="n">
-        <v>25607</v>
+        <v>10151</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>92.03</v>
+        <v>57.98</v>
       </c>
       <c r="B178" t="n">
-        <v>26675</v>
+        <v>19731</v>
       </c>
       <c r="C178" t="n">
-        <v>94.31999999999999</v>
+        <v>58.53</v>
       </c>
       <c r="D178" t="n">
-        <v>17390</v>
+        <v>14353</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>107.08</v>
+        <v>58.1</v>
       </c>
       <c r="B179" t="n">
-        <v>41566</v>
+        <v>18465</v>
       </c>
       <c r="C179" t="n">
-        <v>107.31</v>
+        <v>54.51</v>
       </c>
       <c r="D179" t="n">
-        <v>10588</v>
+        <v>23533</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>93.42</v>
+        <v>58.23</v>
       </c>
       <c r="B180" t="n">
-        <v>29228</v>
+        <v>19831</v>
       </c>
       <c r="C180" t="n">
-        <v>93.84</v>
+        <v>59.83</v>
       </c>
       <c r="D180" t="n">
-        <v>22729</v>
+        <v>14114</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>111.21</v>
+        <v>59.17</v>
       </c>
       <c r="B181" t="n">
-        <v>29061</v>
+        <v>21176</v>
       </c>
       <c r="C181" t="n">
-        <v>111.9</v>
+        <v>61.58</v>
       </c>
       <c r="D181" t="n">
-        <v>25467</v>
+        <v>20426</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>112.32</v>
+        <v>59.23</v>
       </c>
       <c r="B182" t="n">
-        <v>26828</v>
+        <v>22110</v>
       </c>
       <c r="C182" t="n">
-        <v>112.56</v>
+        <v>46.38</v>
       </c>
       <c r="D182" t="n">
-        <v>17849</v>
+        <v>18748</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>113.41</v>
+        <v>59.84</v>
       </c>
       <c r="B183" t="n">
-        <v>25093</v>
+        <v>20584</v>
       </c>
       <c r="C183" t="n">
-        <v>110.32</v>
+        <v>53.43</v>
       </c>
       <c r="D183" t="n">
-        <v>16906</v>
+        <v>13882</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>106.3</v>
+        <v>60.07</v>
       </c>
       <c r="B184" t="n">
-        <v>42385</v>
+        <v>21709</v>
       </c>
       <c r="C184" t="n">
-        <v>103.82</v>
+        <v>51.34</v>
       </c>
       <c r="D184" t="n">
-        <v>16737</v>
+        <v>22647</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>106.39</v>
+        <v>60.25</v>
       </c>
       <c r="B185" t="n">
-        <v>45487</v>
+        <v>20752</v>
       </c>
       <c r="C185" t="n">
-        <v>104.82</v>
+        <v>52.22</v>
       </c>
       <c r="D185" t="n">
-        <v>17883</v>
+        <v>24356</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>112.94</v>
+        <v>60.57</v>
       </c>
       <c r="B186" t="n">
-        <v>25321</v>
+        <v>20708</v>
       </c>
       <c r="C186" t="n">
-        <v>108.85</v>
+        <v>53.69</v>
       </c>
       <c r="D186" t="n">
-        <v>19289</v>
+        <v>14611</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>119.91</v>
+        <v>60.77</v>
       </c>
       <c r="B187" t="n">
-        <v>22486</v>
+        <v>18721</v>
       </c>
       <c r="C187" t="n">
-        <v>124.68</v>
+        <v>53.88</v>
       </c>
       <c r="D187" t="n">
-        <v>12784</v>
+        <v>24256</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>93.48999999999999</v>
+        <v>60.86</v>
       </c>
       <c r="B188" t="n">
-        <v>28083</v>
+        <v>18946</v>
       </c>
       <c r="C188" t="n">
-        <v>94.45</v>
+        <v>61.21</v>
       </c>
       <c r="D188" t="n">
-        <v>25295</v>
+        <v>22762</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>111.2</v>
+        <v>62.03</v>
       </c>
       <c r="B189" t="n">
-        <v>27386</v>
+        <v>20673</v>
       </c>
       <c r="C189" t="n">
-        <v>110.34</v>
+        <v>57.67</v>
       </c>
       <c r="D189" t="n">
-        <v>13025</v>
+        <v>28907</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>100.46</v>
+        <v>62.12</v>
       </c>
       <c r="B190" t="n">
-        <v>45048</v>
+        <v>19444</v>
       </c>
       <c r="C190" t="n">
-        <v>103.61</v>
+        <v>49.64</v>
       </c>
       <c r="D190" t="n">
-        <v>10732</v>
+        <v>18298</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>114.41</v>
+        <v>62.17</v>
       </c>
       <c r="B191" t="n">
-        <v>24803</v>
+        <v>21745</v>
       </c>
       <c r="C191" t="n">
-        <v>114.57</v>
+        <v>46.58</v>
       </c>
       <c r="D191" t="n">
-        <v>29396</v>
+        <v>19105</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>109.61</v>
+        <v>62.9</v>
       </c>
       <c r="B192" t="n">
-        <v>33953</v>
+        <v>20589</v>
       </c>
       <c r="C192" t="n">
-        <v>105.33</v>
+        <v>73.19</v>
       </c>
       <c r="D192" t="n">
-        <v>19711</v>
+        <v>16121</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>108.92</v>
+        <v>63.23</v>
       </c>
       <c r="B193" t="n">
-        <v>36339</v>
+        <v>21315</v>
       </c>
       <c r="C193" t="n">
-        <v>106.06</v>
+        <v>62.87</v>
       </c>
       <c r="D193" t="n">
-        <v>27365</v>
+        <v>17053</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>90.69</v>
+        <v>63.24</v>
       </c>
       <c r="B194" t="n">
-        <v>21483</v>
+        <v>20744</v>
       </c>
       <c r="C194" t="n">
-        <v>93.69</v>
+        <v>75.56</v>
       </c>
       <c r="D194" t="n">
-        <v>27138</v>
+        <v>11467</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>95.25</v>
+        <v>64.34</v>
       </c>
       <c r="B195" t="n">
-        <v>34961</v>
+        <v>21511</v>
       </c>
       <c r="C195" t="n">
-        <v>98.20999999999999</v>
+        <v>65.47</v>
       </c>
       <c r="D195" t="n">
-        <v>14512</v>
+        <v>18002</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>107.32</v>
+        <v>65.28</v>
       </c>
       <c r="B196" t="n">
-        <v>40805</v>
+        <v>21264</v>
       </c>
       <c r="C196" t="n">
-        <v>110.77</v>
+        <v>75.47</v>
       </c>
       <c r="D196" t="n">
-        <v>20288</v>
+        <v>17715</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>107.74</v>
+        <v>65.98999999999999</v>
       </c>
       <c r="B197" t="n">
-        <v>40876</v>
+        <v>21989</v>
       </c>
       <c r="C197" t="n">
-        <v>108.69</v>
+        <v>70.08</v>
       </c>
       <c r="D197" t="n">
-        <v>10925</v>
+        <v>12658</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>92.09</v>
+        <v>66.34</v>
       </c>
       <c r="B198" t="n">
-        <v>29706</v>
+        <v>19807</v>
       </c>
       <c r="C198" t="n">
-        <v>89.59999999999999</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="D198" t="n">
-        <v>21040</v>
+        <v>26901</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>107.66</v>
+        <v>67.3</v>
       </c>
       <c r="B199" t="n">
-        <v>38436</v>
+        <v>20713</v>
       </c>
       <c r="C199" t="n">
-        <v>105.49</v>
+        <v>68.95999999999999</v>
       </c>
       <c r="D199" t="n">
-        <v>24719</v>
+        <v>29631</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>107.29</v>
+        <v>67.58</v>
       </c>
       <c r="B200" t="n">
-        <v>41162</v>
+        <v>20324</v>
       </c>
       <c r="C200" t="n">
-        <v>109.8</v>
+        <v>63.82</v>
       </c>
       <c r="D200" t="n">
-        <v>27421</v>
+        <v>10611</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>113.62</v>
+        <v>67.61</v>
       </c>
       <c r="B201" t="n">
-        <v>23209</v>
+        <v>19842</v>
       </c>
       <c r="C201" t="n">
-        <v>112.64</v>
+        <v>63.66</v>
       </c>
       <c r="D201" t="n">
-        <v>25977</v>
+        <v>27173</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>106.42</v>
+        <v>68.91</v>
       </c>
       <c r="B202" t="n">
-        <v>45845</v>
+        <v>20088</v>
       </c>
       <c r="C202" t="n">
-        <v>104.67</v>
+        <v>66.84</v>
       </c>
       <c r="D202" t="n">
-        <v>14059</v>
+        <v>17537</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>105.92</v>
+        <v>69.95</v>
       </c>
       <c r="B203" t="n">
-        <v>44709</v>
+        <v>21411</v>
       </c>
       <c r="C203" t="n">
-        <v>103.31</v>
+        <v>75.36</v>
       </c>
       <c r="D203" t="n">
-        <v>24188</v>
+        <v>22776</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>90.31999999999999</v>
+        <v>70.02</v>
       </c>
       <c r="B204" t="n">
-        <v>24664</v>
+        <v>20080</v>
       </c>
       <c r="C204" t="n">
-        <v>91.88</v>
+        <v>60.7</v>
       </c>
       <c r="D204" t="n">
-        <v>25051</v>
+        <v>25851</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>106.88</v>
+        <v>70.51000000000001</v>
       </c>
       <c r="B205" t="n">
-        <v>42863</v>
+        <v>19827</v>
       </c>
       <c r="C205" t="n">
-        <v>107.82</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="D205" t="n">
-        <v>18291</v>
+        <v>10668</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>125.29</v>
+        <v>71.87</v>
       </c>
       <c r="B206" t="n">
-        <v>24092</v>
+        <v>20993</v>
       </c>
       <c r="C206" t="n">
-        <v>123.69</v>
+        <v>80.76000000000001</v>
       </c>
       <c r="D206" t="n">
-        <v>16217</v>
+        <v>15678</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>114.36</v>
+        <v>72.17</v>
       </c>
       <c r="B207" t="n">
-        <v>25458</v>
+        <v>19817</v>
       </c>
       <c r="C207" t="n">
-        <v>111.11</v>
+        <v>76.81999999999999</v>
       </c>
       <c r="D207" t="n">
-        <v>18664</v>
+        <v>24669</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>177.07</v>
+        <v>72.28</v>
       </c>
       <c r="B208" t="n">
-        <v>23179</v>
+        <v>20839</v>
       </c>
       <c r="C208" t="n">
-        <v>176.8</v>
+        <v>61.85</v>
       </c>
       <c r="D208" t="n">
-        <v>27687</v>
+        <v>25791</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>101.36</v>
+        <v>72.8</v>
       </c>
       <c r="B209" t="n">
-        <v>43885</v>
+        <v>21703</v>
       </c>
       <c r="C209" t="n">
-        <v>101.14</v>
+        <v>85.26000000000001</v>
       </c>
       <c r="D209" t="n">
-        <v>13472</v>
+        <v>26543</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>93.91</v>
+        <v>74.23999999999999</v>
       </c>
       <c r="B210" t="n">
-        <v>30708</v>
+        <v>20508</v>
       </c>
       <c r="C210" t="n">
-        <v>92.23999999999999</v>
+        <v>66.66</v>
       </c>
       <c r="D210" t="n">
-        <v>13573</v>
+        <v>20539</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>114.54</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="B211" t="n">
-        <v>23363</v>
+        <v>19995</v>
       </c>
       <c r="C211" t="n">
-        <v>111.79</v>
+        <v>82.42</v>
       </c>
       <c r="D211" t="n">
-        <v>28718</v>
+        <v>17498</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>54.89</v>
+        <v>74.39</v>
       </c>
       <c r="B212" t="n">
-        <v>24955</v>
+        <v>19535</v>
       </c>
       <c r="C212" t="n">
-        <v>55.41</v>
+        <v>62.28</v>
       </c>
       <c r="D212" t="n">
-        <v>15560</v>
+        <v>29587</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>80.13</v>
+        <v>75.25</v>
       </c>
       <c r="B213" t="n">
-        <v>22134</v>
+        <v>19219</v>
       </c>
       <c r="C213" t="n">
-        <v>82.33</v>
+        <v>70.41</v>
       </c>
       <c r="D213" t="n">
-        <v>25307</v>
+        <v>14805</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>108.1</v>
+        <v>75.48999999999999</v>
       </c>
       <c r="B214" t="n">
-        <v>37617</v>
+        <v>21114</v>
       </c>
       <c r="C214" t="n">
-        <v>104.68</v>
+        <v>67.59</v>
       </c>
       <c r="D214" t="n">
-        <v>27451</v>
+        <v>12391</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>97.22</v>
+        <v>76.16</v>
       </c>
       <c r="B215" t="n">
-        <v>38494</v>
+        <v>20911</v>
       </c>
       <c r="C215" t="n">
-        <v>96.39</v>
+        <v>82.19</v>
       </c>
       <c r="D215" t="n">
-        <v>24676</v>
+        <v>23673</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>108.56</v>
+        <v>76.18000000000001</v>
       </c>
       <c r="B216" t="n">
-        <v>36629</v>
+        <v>20059</v>
       </c>
       <c r="C216" t="n">
-        <v>109.27</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="D216" t="n">
-        <v>10250</v>
+        <v>26889</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>98.76000000000001</v>
+        <v>76.7</v>
       </c>
       <c r="B217" t="n">
-        <v>41137</v>
+        <v>20323</v>
       </c>
       <c r="C217" t="n">
-        <v>96.76000000000001</v>
+        <v>87.06999999999999</v>
       </c>
       <c r="D217" t="n">
-        <v>16752</v>
+        <v>15229</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>103.46</v>
+        <v>77.20999999999999</v>
       </c>
       <c r="B218" t="n">
-        <v>44565</v>
+        <v>19933</v>
       </c>
       <c r="C218" t="n">
-        <v>106.95</v>
+        <v>78.27</v>
       </c>
       <c r="D218" t="n">
-        <v>21250</v>
+        <v>12810</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>88.98</v>
+        <v>77.27</v>
       </c>
       <c r="B219" t="n">
-        <v>24780</v>
+        <v>20735</v>
       </c>
       <c r="C219" t="n">
-        <v>89.34</v>
+        <v>94.69</v>
       </c>
       <c r="D219" t="n">
-        <v>27331</v>
+        <v>24772</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>105.87</v>
+        <v>77.39</v>
       </c>
       <c r="B220" t="n">
-        <v>42908</v>
+        <v>20184</v>
       </c>
       <c r="C220" t="n">
-        <v>105.96</v>
+        <v>64.03</v>
       </c>
       <c r="D220" t="n">
-        <v>18292</v>
+        <v>21323</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>23.06</v>
+        <v>77.84</v>
       </c>
       <c r="B221" t="n">
-        <v>23181</v>
+        <v>19750</v>
       </c>
       <c r="C221" t="n">
-        <v>23.17</v>
+        <v>61.62</v>
       </c>
       <c r="D221" t="n">
-        <v>14830</v>
+        <v>13853</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>108.42</v>
+        <v>78.09</v>
       </c>
       <c r="B222" t="n">
-        <v>36225</v>
+        <v>20878</v>
       </c>
       <c r="C222" t="n">
-        <v>109.86</v>
+        <v>92.41</v>
       </c>
       <c r="D222" t="n">
-        <v>22442</v>
+        <v>20204</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>33.52</v>
+        <v>78.31999999999999</v>
       </c>
       <c r="B223" t="n">
-        <v>24442</v>
+        <v>19164</v>
       </c>
       <c r="C223" t="n">
-        <v>34.58</v>
+        <v>86.66</v>
       </c>
       <c r="D223" t="n">
-        <v>27384</v>
+        <v>11152</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>92.97</v>
+        <v>79.26000000000001</v>
       </c>
       <c r="B224" t="n">
-        <v>25966</v>
+        <v>20694</v>
       </c>
       <c r="C224" t="n">
-        <v>91.33</v>
+        <v>71.54000000000001</v>
       </c>
       <c r="D224" t="n">
-        <v>15320</v>
+        <v>20499</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>108.55</v>
+        <v>79.91</v>
       </c>
       <c r="B225" t="n">
-        <v>35217</v>
+        <v>20550</v>
       </c>
       <c r="C225" t="n">
-        <v>109.12</v>
+        <v>88.73999999999999</v>
       </c>
       <c r="D225" t="n">
-        <v>20470</v>
+        <v>13569</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>93.98</v>
+        <v>80.11</v>
       </c>
       <c r="B226" t="n">
-        <v>29032</v>
+        <v>20457</v>
       </c>
       <c r="C226" t="n">
-        <v>97.45</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="D226" t="n">
-        <v>26662</v>
+        <v>21608</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>105.99</v>
+        <v>80.29000000000001</v>
       </c>
       <c r="B227" t="n">
-        <v>43032</v>
+        <v>20180</v>
       </c>
       <c r="C227" t="n">
-        <v>102.03</v>
+        <v>99.26000000000001</v>
       </c>
       <c r="D227" t="n">
-        <v>22675</v>
+        <v>21282</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>103.93</v>
+        <v>80.59</v>
       </c>
       <c r="B228" t="n">
-        <v>45174</v>
+        <v>19998</v>
       </c>
       <c r="C228" t="n">
-        <v>100.49</v>
+        <v>75.08</v>
       </c>
       <c r="D228" t="n">
-        <v>16967</v>
+        <v>28281</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>96.65000000000001</v>
+        <v>81.62</v>
       </c>
       <c r="B229" t="n">
-        <v>35690</v>
+        <v>21287</v>
       </c>
       <c r="C229" t="n">
-        <v>101.33</v>
+        <v>78.87</v>
       </c>
       <c r="D229" t="n">
-        <v>21716</v>
+        <v>22719</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>38.45</v>
+        <v>81.67</v>
       </c>
       <c r="B230" t="n">
-        <v>24204</v>
+        <v>20207</v>
       </c>
       <c r="C230" t="n">
-        <v>37.28</v>
+        <v>102.75</v>
       </c>
       <c r="D230" t="n">
-        <v>28791</v>
+        <v>26417</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>92.29000000000001</v>
+        <v>81.86</v>
       </c>
       <c r="B231" t="n">
-        <v>24650</v>
+        <v>19491</v>
       </c>
       <c r="C231" t="n">
-        <v>94.73</v>
+        <v>82.79000000000001</v>
       </c>
       <c r="D231" t="n">
-        <v>27028</v>
+        <v>16987</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>94.61</v>
+        <v>82.23</v>
       </c>
       <c r="B232" t="n">
-        <v>33952</v>
+        <v>20589</v>
       </c>
       <c r="C232" t="n">
-        <v>91.23999999999999</v>
+        <v>75.65000000000001</v>
       </c>
       <c r="D232" t="n">
-        <v>16366</v>
+        <v>20311</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>110.28</v>
+        <v>82.87</v>
       </c>
       <c r="B233" t="n">
-        <v>32509</v>
+        <v>18995</v>
       </c>
       <c r="C233" t="n">
-        <v>109.15</v>
+        <v>85.53</v>
       </c>
       <c r="D233" t="n">
-        <v>18036</v>
+        <v>25804</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>111.81</v>
+        <v>83.12</v>
       </c>
       <c r="B234" t="n">
-        <v>28954</v>
+        <v>20824</v>
       </c>
       <c r="C234" t="n">
-        <v>113.58</v>
+        <v>66.48999999999999</v>
       </c>
       <c r="D234" t="n">
-        <v>15797</v>
+        <v>22727</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>108.6</v>
+        <v>83.27</v>
       </c>
       <c r="B235" t="n">
-        <v>35818</v>
+        <v>20364</v>
       </c>
       <c r="C235" t="n">
-        <v>108.47</v>
+        <v>77.81</v>
       </c>
       <c r="D235" t="n">
-        <v>17686</v>
+        <v>13031</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>110.55</v>
+        <v>83.44</v>
       </c>
       <c r="B236" t="n">
-        <v>30373</v>
+        <v>19973</v>
       </c>
       <c r="C236" t="n">
-        <v>108.8</v>
+        <v>90.61</v>
       </c>
       <c r="D236" t="n">
-        <v>22295</v>
+        <v>12027</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>103.48</v>
+        <v>83.89</v>
       </c>
       <c r="B237" t="n">
-        <v>45158</v>
+        <v>20352</v>
       </c>
       <c r="C237" t="n">
-        <v>102.03</v>
+        <v>99.95999999999999</v>
       </c>
       <c r="D237" t="n">
-        <v>15489</v>
+        <v>29206</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>100.53</v>
+        <v>84.17</v>
       </c>
       <c r="B238" t="n">
-        <v>46523</v>
+        <v>20384</v>
       </c>
       <c r="C238" t="n">
-        <v>100.14</v>
+        <v>93.84999999999999</v>
       </c>
       <c r="D238" t="n">
-        <v>23092</v>
+        <v>16218</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>113.72</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="B239" t="n">
-        <v>24451</v>
+        <v>19853</v>
       </c>
       <c r="C239" t="n">
-        <v>110.76</v>
+        <v>94.84999999999999</v>
       </c>
       <c r="D239" t="n">
-        <v>13437</v>
+        <v>17027</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>26.73</v>
+        <v>84.51000000000001</v>
       </c>
       <c r="B240" t="n">
-        <v>24421</v>
+        <v>20051</v>
       </c>
       <c r="C240" t="n">
-        <v>26.53</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="D240" t="n">
-        <v>27190</v>
+        <v>14343</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>96.25</v>
+        <v>84.69</v>
       </c>
       <c r="B241" t="n">
-        <v>37240</v>
+        <v>20841</v>
       </c>
       <c r="C241" t="n">
-        <v>98.72</v>
+        <v>98.17</v>
       </c>
       <c r="D241" t="n">
-        <v>26608</v>
+        <v>16194</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>109.51</v>
+        <v>85.37</v>
       </c>
       <c r="B242" t="n">
-        <v>33685</v>
+        <v>20573</v>
       </c>
       <c r="C242" t="n">
-        <v>107.86</v>
+        <v>74.72</v>
       </c>
       <c r="D242" t="n">
-        <v>18596</v>
+        <v>15092</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>106.56</v>
+        <v>86.06</v>
       </c>
       <c r="B243" t="n">
-        <v>42405</v>
+        <v>20311</v>
       </c>
       <c r="C243" t="n">
-        <v>110.39</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="D243" t="n">
-        <v>19127</v>
+        <v>24739</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>90.18000000000001</v>
+        <v>86.84999999999999</v>
       </c>
       <c r="B244" t="n">
-        <v>24989</v>
+        <v>20508</v>
       </c>
       <c r="C244" t="n">
-        <v>86.66</v>
+        <v>85.59</v>
       </c>
       <c r="D244" t="n">
-        <v>20958</v>
+        <v>24722</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>108.67</v>
+        <v>87.09</v>
       </c>
       <c r="B245" t="n">
-        <v>35938</v>
+        <v>20671</v>
       </c>
       <c r="C245" t="n">
-        <v>113.03</v>
+        <v>75.64</v>
       </c>
       <c r="D245" t="n">
-        <v>25134</v>
+        <v>22238</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>39.49</v>
+        <v>87.19</v>
       </c>
       <c r="B246" t="n">
-        <v>21663</v>
+        <v>20220</v>
       </c>
       <c r="C246" t="n">
-        <v>40.45</v>
+        <v>82.36</v>
       </c>
       <c r="D246" t="n">
-        <v>15501</v>
+        <v>17043</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>94.28</v>
+        <v>88.31999999999999</v>
       </c>
       <c r="B247" t="n">
-        <v>32162</v>
+        <v>20379</v>
       </c>
       <c r="C247" t="n">
-        <v>92.27</v>
+        <v>75.13</v>
       </c>
       <c r="D247" t="n">
-        <v>15050</v>
+        <v>21597</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>89.93000000000001</v>
+        <v>88.41</v>
       </c>
       <c r="B248" t="n">
-        <v>21948</v>
+        <v>20777</v>
       </c>
       <c r="C248" t="n">
-        <v>90.90000000000001</v>
+        <v>90.37</v>
       </c>
       <c r="D248" t="n">
-        <v>25748</v>
+        <v>17654</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>112.74</v>
+        <v>88.69</v>
       </c>
       <c r="B249" t="n">
-        <v>25905</v>
+        <v>20175</v>
       </c>
       <c r="C249" t="n">
-        <v>110.48</v>
+        <v>66.19</v>
       </c>
       <c r="D249" t="n">
-        <v>22052</v>
+        <v>24114</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>27.55</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="B250" t="n">
-        <v>20731</v>
+        <v>20105</v>
       </c>
       <c r="C250" t="n">
-        <v>28.28</v>
+        <v>97.59</v>
       </c>
       <c r="D250" t="n">
-        <v>15111</v>
+        <v>10629</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>94.8</v>
+        <v>89.55</v>
       </c>
       <c r="B251" t="n">
-        <v>32354</v>
+        <v>20952</v>
       </c>
       <c r="C251" t="n">
-        <v>93.03</v>
+        <v>77.44</v>
       </c>
       <c r="D251" t="n">
-        <v>17820</v>
+        <v>19609</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>101.76</v>
+        <v>89.75</v>
       </c>
       <c r="B252" t="n">
-        <v>45336</v>
+        <v>21698</v>
       </c>
       <c r="C252" t="n">
-        <v>103.43</v>
+        <v>75.08</v>
       </c>
       <c r="D252" t="n">
-        <v>17892</v>
+        <v>15413</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>100.05</v>
+        <v>90.47</v>
       </c>
       <c r="B253" t="n">
-        <v>43527</v>
+        <v>20844</v>
       </c>
       <c r="C253" t="n">
-        <v>99.13</v>
+        <v>89.23999999999999</v>
       </c>
       <c r="D253" t="n">
-        <v>15703</v>
+        <v>15670</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>95.51000000000001</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="B254" t="n">
-        <v>33361</v>
+        <v>21274</v>
       </c>
       <c r="C254" t="n">
-        <v>94.23</v>
+        <v>101.85</v>
       </c>
       <c r="D254" t="n">
-        <v>27128</v>
+        <v>11443</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>114.58</v>
+        <v>91.25</v>
       </c>
       <c r="B255" t="n">
-        <v>25647</v>
+        <v>21329</v>
       </c>
       <c r="C255" t="n">
-        <v>112.48</v>
+        <v>67.95999999999999</v>
       </c>
       <c r="D255" t="n">
-        <v>19189</v>
+        <v>14227</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>113.85</v>
+        <v>91.56999999999999</v>
       </c>
       <c r="B256" t="n">
-        <v>23734</v>
+        <v>21189</v>
       </c>
       <c r="C256" t="n">
-        <v>118.01</v>
+        <v>95.3</v>
       </c>
       <c r="D256" t="n">
-        <v>24942</v>
+        <v>19958</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>94.61</v>
+        <v>92.2</v>
       </c>
       <c r="B257" t="n">
-        <v>31801</v>
+        <v>21737</v>
       </c>
       <c r="C257" t="n">
-        <v>97.45</v>
+        <v>91.34</v>
       </c>
       <c r="D257" t="n">
-        <v>19625</v>
+        <v>13332</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>103.21</v>
+        <v>92.41</v>
       </c>
       <c r="B258" t="n">
-        <v>46483</v>
+        <v>22410</v>
       </c>
       <c r="C258" t="n">
-        <v>102.26</v>
+        <v>92.54000000000001</v>
       </c>
       <c r="D258" t="n">
-        <v>27757</v>
+        <v>29808</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>109.44</v>
+        <v>92.63</v>
       </c>
       <c r="B259" t="n">
-        <v>35444</v>
+        <v>21631</v>
       </c>
       <c r="C259" t="n">
-        <v>113.29</v>
+        <v>97.77</v>
       </c>
       <c r="D259" t="n">
-        <v>19981</v>
+        <v>11559</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>107.68</v>
+        <v>92.81</v>
       </c>
       <c r="B260" t="n">
-        <v>39438</v>
+        <v>22890</v>
       </c>
       <c r="C260" t="n">
-        <v>105</v>
+        <v>80.64</v>
       </c>
       <c r="D260" t="n">
-        <v>21138</v>
+        <v>11887</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>158.55</v>
+        <v>92.84</v>
       </c>
       <c r="B261" t="n">
-        <v>24442</v>
+        <v>21764</v>
       </c>
       <c r="C261" t="n">
-        <v>164.01</v>
+        <v>80.56999999999999</v>
       </c>
       <c r="D261" t="n">
-        <v>29367</v>
+        <v>25648</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>107.99</v>
+        <v>93.31</v>
       </c>
       <c r="B262" t="n">
-        <v>39216</v>
+        <v>22972</v>
       </c>
       <c r="C262" t="n">
-        <v>106.02</v>
+        <v>77.23</v>
       </c>
       <c r="D262" t="n">
-        <v>21909</v>
+        <v>29408</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>112.45</v>
+        <v>93.84</v>
       </c>
       <c r="B263" t="n">
-        <v>26693</v>
+        <v>23729</v>
       </c>
       <c r="C263" t="n">
-        <v>110.54</v>
+        <v>93.36</v>
       </c>
       <c r="D263" t="n">
-        <v>23836</v>
+        <v>19473</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>57.91</v>
+        <v>93.95</v>
       </c>
       <c r="B264" t="n">
-        <v>24985</v>
+        <v>22880</v>
       </c>
       <c r="C264" t="n">
-        <v>58.26</v>
+        <v>81.79000000000001</v>
       </c>
       <c r="D264" t="n">
-        <v>19689</v>
+        <v>28195</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>9.15</v>
+        <v>94.53</v>
       </c>
       <c r="B265" t="n">
-        <v>21002</v>
+        <v>25251</v>
       </c>
       <c r="C265" t="n">
-        <v>10.02</v>
+        <v>102.04</v>
       </c>
       <c r="D265" t="n">
-        <v>17925</v>
+        <v>26943</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>94.16</v>
+        <v>94.59</v>
       </c>
       <c r="B266" t="n">
-        <v>30376</v>
+        <v>25155</v>
       </c>
       <c r="C266" t="n">
-        <v>95.23</v>
+        <v>92.95999999999999</v>
       </c>
       <c r="D266" t="n">
-        <v>25783</v>
+        <v>29685</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>33.04</v>
+        <v>94.7</v>
       </c>
       <c r="B267" t="n">
-        <v>23451</v>
+        <v>24704</v>
       </c>
       <c r="C267" t="n">
-        <v>33.28</v>
+        <v>95.75</v>
       </c>
       <c r="D267" t="n">
-        <v>14099</v>
+        <v>29396</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>110.13</v>
+        <v>95.79000000000001</v>
       </c>
       <c r="B268" t="n">
-        <v>28699</v>
+        <v>26591</v>
       </c>
       <c r="C268" t="n">
-        <v>108.22</v>
+        <v>76.83</v>
       </c>
       <c r="D268" t="n">
-        <v>21994</v>
+        <v>21519</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>109.82</v>
+        <v>95.94</v>
       </c>
       <c r="B269" t="n">
-        <v>33387</v>
+        <v>25749</v>
       </c>
       <c r="C269" t="n">
-        <v>108.2</v>
+        <v>88.69</v>
       </c>
       <c r="D269" t="n">
-        <v>24033</v>
+        <v>26678</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>92.38</v>
+        <v>96.28</v>
       </c>
       <c r="B270" t="n">
-        <v>23923</v>
+        <v>27761</v>
       </c>
       <c r="C270" t="n">
-        <v>93.48999999999999</v>
+        <v>105.04</v>
       </c>
       <c r="D270" t="n">
-        <v>27197</v>
+        <v>17026</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>90.37</v>
+        <v>96.76000000000001</v>
       </c>
       <c r="B271" t="n">
-        <v>23467</v>
+        <v>27996</v>
       </c>
       <c r="C271" t="n">
-        <v>89.25</v>
+        <v>79.27</v>
       </c>
       <c r="D271" t="n">
-        <v>24117</v>
+        <v>10729</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>149.63</v>
+        <v>97.56</v>
       </c>
       <c r="B272" t="n">
-        <v>25685</v>
+        <v>30051</v>
       </c>
       <c r="C272" t="n">
-        <v>145.18</v>
+        <v>107.59</v>
       </c>
       <c r="D272" t="n">
-        <v>18786</v>
+        <v>13955</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>98.67</v>
+        <v>97.67</v>
       </c>
       <c r="B273" t="n">
-        <v>45027</v>
+        <v>30738</v>
       </c>
       <c r="C273" t="n">
-        <v>95.2</v>
+        <v>105.44</v>
       </c>
       <c r="D273" t="n">
-        <v>20310</v>
+        <v>10084</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>62.26</v>
+        <v>98.01000000000001</v>
       </c>
       <c r="B274" t="n">
-        <v>20908</v>
+        <v>31673</v>
       </c>
       <c r="C274" t="n">
-        <v>63.25</v>
+        <v>85.61</v>
       </c>
       <c r="D274" t="n">
-        <v>10353</v>
+        <v>17445</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>92.79000000000001</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="B275" t="n">
-        <v>27797</v>
+        <v>30687</v>
       </c>
       <c r="C275" t="n">
-        <v>89.40000000000001</v>
+        <v>100.38</v>
       </c>
       <c r="D275" t="n">
-        <v>25645</v>
+        <v>21180</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>91.90000000000001</v>
+        <v>98.52</v>
       </c>
       <c r="B276" t="n">
-        <v>26813</v>
+        <v>31856</v>
       </c>
       <c r="C276" t="n">
-        <v>91.34999999999999</v>
+        <v>93.34999999999999</v>
       </c>
       <c r="D276" t="n">
-        <v>11609</v>
+        <v>27331</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>101.65</v>
+        <v>99.01000000000001</v>
       </c>
       <c r="B277" t="n">
-        <v>46737</v>
+        <v>34051</v>
       </c>
       <c r="C277" t="n">
-        <v>105.05</v>
+        <v>110.27</v>
       </c>
       <c r="D277" t="n">
-        <v>17785</v>
+        <v>18492</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>97.51000000000001</v>
+        <v>99.56</v>
       </c>
       <c r="B278" t="n">
-        <v>39894</v>
+        <v>34580</v>
       </c>
       <c r="C278" t="n">
-        <v>95.29000000000001</v>
+        <v>75.52</v>
       </c>
       <c r="D278" t="n">
-        <v>29000</v>
+        <v>23720</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>54.6</v>
+        <v>100.13</v>
       </c>
       <c r="B279" t="n">
-        <v>24395</v>
+        <v>35549</v>
       </c>
       <c r="C279" t="n">
-        <v>54.22</v>
+        <v>92.48</v>
       </c>
       <c r="D279" t="n">
-        <v>18136</v>
+        <v>25314</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>107.23</v>
+        <v>100.18</v>
       </c>
       <c r="B280" t="n">
-        <v>40436</v>
+        <v>35572</v>
       </c>
       <c r="C280" t="n">
-        <v>103.33</v>
+        <v>117.97</v>
       </c>
       <c r="D280" t="n">
-        <v>21749</v>
+        <v>25975</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>21.43</v>
+        <v>100.97</v>
       </c>
       <c r="B281" t="n">
-        <v>22071</v>
+        <v>35536</v>
       </c>
       <c r="C281" t="n">
-        <v>23.75</v>
+        <v>111.02</v>
       </c>
       <c r="D281" t="n">
-        <v>16660</v>
+        <v>26155</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>101.71</v>
+        <v>102.14</v>
       </c>
       <c r="B282" t="n">
-        <v>50561</v>
+        <v>37941</v>
       </c>
       <c r="C282" t="n">
-        <v>103.65</v>
+        <v>102.7</v>
       </c>
       <c r="D282" t="n">
-        <v>11476</v>
+        <v>29883</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>127.89</v>
+        <v>102.32</v>
       </c>
       <c r="B283" t="n">
-        <v>21295</v>
+        <v>38036</v>
       </c>
       <c r="C283" t="n">
-        <v>123.28</v>
+        <v>76.29000000000001</v>
       </c>
       <c r="D283" t="n">
-        <v>25835</v>
+        <v>26838</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>112.07</v>
+        <v>102.42</v>
       </c>
       <c r="B284" t="n">
-        <v>26502</v>
+        <v>38148</v>
       </c>
       <c r="C284" t="n">
-        <v>115.28</v>
+        <v>101.67</v>
       </c>
       <c r="D284" t="n">
-        <v>29328</v>
+        <v>11677</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>108.06</v>
+        <v>103.64</v>
       </c>
       <c r="B285" t="n">
-        <v>38613</v>
+        <v>39007</v>
       </c>
       <c r="C285" t="n">
-        <v>109.98</v>
+        <v>103.11</v>
       </c>
       <c r="D285" t="n">
-        <v>26311</v>
+        <v>17423</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>150.99</v>
+        <v>103.82</v>
       </c>
       <c r="B286" t="n">
-        <v>22325</v>
+        <v>37426</v>
       </c>
       <c r="C286" t="n">
-        <v>145.21</v>
+        <v>109.8</v>
       </c>
       <c r="D286" t="n">
-        <v>18103</v>
+        <v>29868</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>90.47</v>
+        <v>103.89</v>
       </c>
       <c r="B287" t="n">
-        <v>24422</v>
+        <v>37306</v>
       </c>
       <c r="C287" t="n">
-        <v>92.58</v>
+        <v>101.16</v>
       </c>
       <c r="D287" t="n">
-        <v>20274</v>
+        <v>23177</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>70.39</v>
+        <v>103.99</v>
       </c>
       <c r="B288" t="n">
-        <v>23263</v>
+        <v>38599</v>
       </c>
       <c r="C288" t="n">
-        <v>72.7</v>
+        <v>118.29</v>
       </c>
       <c r="D288" t="n">
-        <v>28741</v>
+        <v>20578</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>105.48</v>
+        <v>104.05</v>
       </c>
       <c r="B289" t="n">
-        <v>45295</v>
+        <v>37633</v>
       </c>
       <c r="C289" t="n">
-        <v>104.27</v>
+        <v>120.77</v>
       </c>
       <c r="D289" t="n">
-        <v>12829</v>
+        <v>12089</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>104.39</v>
+        <v>104.28</v>
       </c>
       <c r="B290" t="n">
-        <v>45729</v>
+        <v>36578</v>
       </c>
       <c r="C290" t="n">
-        <v>104.92</v>
+        <v>101.97</v>
       </c>
       <c r="D290" t="n">
-        <v>16921</v>
+        <v>25052</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>100.31</v>
+        <v>105.34</v>
       </c>
       <c r="B291" t="n">
-        <v>47225</v>
+        <v>36177</v>
       </c>
       <c r="C291" t="n">
-        <v>98.98999999999999</v>
+        <v>97.98</v>
       </c>
       <c r="D291" t="n">
-        <v>23593</v>
+        <v>21033</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>108.19</v>
+        <v>106.13</v>
       </c>
       <c r="B292" t="n">
-        <v>38333</v>
+        <v>34463</v>
       </c>
       <c r="C292" t="n">
-        <v>110.66</v>
+        <v>127.43</v>
       </c>
       <c r="D292" t="n">
-        <v>26080</v>
+        <v>25116</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>114.88</v>
+        <v>106.44</v>
       </c>
       <c r="B293" t="n">
-        <v>24023</v>
+        <v>34845</v>
       </c>
       <c r="C293" t="n">
-        <v>110.58</v>
+        <v>107.04</v>
       </c>
       <c r="D293" t="n">
-        <v>19060</v>
+        <v>10829</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>104.1</v>
+        <v>106.71</v>
       </c>
       <c r="B294" t="n">
-        <v>46489</v>
+        <v>33160</v>
       </c>
       <c r="C294" t="n">
-        <v>103.14</v>
+        <v>114.94</v>
       </c>
       <c r="D294" t="n">
-        <v>14733</v>
+        <v>29870</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>98.95999999999999</v>
+        <v>106.99</v>
       </c>
       <c r="B295" t="n">
-        <v>43148</v>
+        <v>33152</v>
       </c>
       <c r="C295" t="n">
-        <v>95.53</v>
+        <v>107.98</v>
       </c>
       <c r="D295" t="n">
-        <v>24636</v>
+        <v>19093</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>114.32</v>
+        <v>107.17</v>
       </c>
       <c r="B296" t="n">
-        <v>25221</v>
+        <v>32608</v>
       </c>
       <c r="C296" t="n">
-        <v>116.8</v>
+        <v>89.29000000000001</v>
       </c>
       <c r="D296" t="n">
-        <v>16631</v>
+        <v>23130</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>107.88</v>
+        <v>107.83</v>
       </c>
       <c r="B297" t="n">
-        <v>38377</v>
+        <v>30277</v>
       </c>
       <c r="C297" t="n">
-        <v>103.69</v>
+        <v>114.37</v>
       </c>
       <c r="D297" t="n">
-        <v>21141</v>
+        <v>22292</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>109.33</v>
+        <v>108.18</v>
       </c>
       <c r="B298" t="n">
-        <v>33969</v>
+        <v>29949</v>
       </c>
       <c r="C298" t="n">
-        <v>111.62</v>
+        <v>106.05</v>
       </c>
       <c r="D298" t="n">
-        <v>20674</v>
+        <v>17835</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>91.51000000000001</v>
+        <v>108.51</v>
       </c>
       <c r="B299" t="n">
-        <v>24219</v>
+        <v>29513</v>
       </c>
       <c r="C299" t="n">
-        <v>90.03</v>
+        <v>98.97</v>
       </c>
       <c r="D299" t="n">
-        <v>26671</v>
+        <v>15538</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>142.16</v>
+        <v>108.72</v>
       </c>
       <c r="B300" t="n">
-        <v>23805</v>
+        <v>28259</v>
       </c>
       <c r="C300" t="n">
-        <v>137.75</v>
+        <v>117.35</v>
       </c>
       <c r="D300" t="n">
-        <v>25719</v>
+        <v>26408</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>90.34999999999999</v>
+        <v>109.58</v>
       </c>
       <c r="B301" t="n">
-        <v>25665</v>
+        <v>27089</v>
       </c>
       <c r="C301" t="n">
-        <v>88.72</v>
+        <v>130.19</v>
       </c>
       <c r="D301" t="n">
-        <v>12537</v>
+        <v>20901</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>93.01000000000001</v>
+        <v>109.82</v>
       </c>
       <c r="B302" t="n">
-        <v>28244</v>
+        <v>26890</v>
       </c>
       <c r="C302" t="n">
-        <v>96.14</v>
+        <v>128.59</v>
       </c>
       <c r="D302" t="n">
-        <v>10160</v>
+        <v>20824</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>112.13</v>
+        <v>110.82</v>
       </c>
       <c r="B303" t="n">
-        <v>25266</v>
+        <v>25522</v>
       </c>
       <c r="C303" t="n">
-        <v>110.32</v>
+        <v>103.62</v>
       </c>
       <c r="D303" t="n">
-        <v>27683</v>
+        <v>13120</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>110.36</v>
+        <v>110.9</v>
       </c>
       <c r="B304" t="n">
-        <v>31212</v>
+        <v>24344</v>
       </c>
       <c r="C304" t="n">
-        <v>113.11</v>
+        <v>109.48</v>
       </c>
       <c r="D304" t="n">
-        <v>15551</v>
+        <v>17235</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>108.86</v>
+        <v>111.19</v>
       </c>
       <c r="B305" t="n">
-        <v>35993</v>
+        <v>25448</v>
       </c>
       <c r="C305" t="n">
-        <v>108.54</v>
+        <v>110.43</v>
       </c>
       <c r="D305" t="n">
-        <v>29290</v>
+        <v>20512</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>97.33</v>
+        <v>111.41</v>
       </c>
       <c r="B306" t="n">
-        <v>40513</v>
+        <v>23596</v>
       </c>
       <c r="C306" t="n">
-        <v>95.34</v>
+        <v>114.72</v>
       </c>
       <c r="D306" t="n">
-        <v>14212</v>
+        <v>20013</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>177.24</v>
+        <v>111.78</v>
       </c>
       <c r="B307" t="n">
-        <v>23023</v>
+        <v>25551</v>
       </c>
       <c r="C307" t="n">
-        <v>177.76</v>
+        <v>114.41</v>
       </c>
       <c r="D307" t="n">
-        <v>24166</v>
+        <v>21111</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>106.75</v>
+        <v>111.78</v>
       </c>
       <c r="B308" t="n">
-        <v>43918</v>
+        <v>24682</v>
       </c>
       <c r="C308" t="n">
-        <v>108.07</v>
+        <v>100.63</v>
       </c>
       <c r="D308" t="n">
-        <v>22688</v>
+        <v>17500</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>105.18</v>
+        <v>112.06</v>
       </c>
       <c r="B309" t="n">
-        <v>44554</v>
+        <v>21647</v>
       </c>
       <c r="C309" t="n">
-        <v>108</v>
+        <v>131.76</v>
       </c>
       <c r="D309" t="n">
-        <v>17542</v>
+        <v>16413</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>112.56</v>
+        <v>112.17</v>
       </c>
       <c r="B310" t="n">
-        <v>27159</v>
+        <v>22882</v>
       </c>
       <c r="C310" t="n">
-        <v>114.62</v>
+        <v>134.99</v>
       </c>
       <c r="D310" t="n">
-        <v>17237</v>
+        <v>17121</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>103.91</v>
+        <v>112.25</v>
       </c>
       <c r="B311" t="n">
-        <v>45764</v>
+        <v>22083</v>
       </c>
       <c r="C311" t="n">
-        <v>103.4</v>
+        <v>131.43</v>
       </c>
       <c r="D311" t="n">
-        <v>13180</v>
+        <v>21774</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>96.61</v>
+        <v>112.62</v>
       </c>
       <c r="B312" t="n">
-        <v>38982</v>
+        <v>23497</v>
       </c>
       <c r="C312" t="n">
-        <v>99.95</v>
+        <v>88.76000000000001</v>
       </c>
       <c r="D312" t="n">
-        <v>28726</v>
+        <v>28460</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>113.45</v>
+        <v>112.67</v>
       </c>
       <c r="B313" t="n">
-        <v>23704</v>
+        <v>23835</v>
       </c>
       <c r="C313" t="n">
-        <v>117.28</v>
+        <v>101.14</v>
       </c>
       <c r="D313" t="n">
-        <v>16226</v>
+        <v>13315</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>91.13</v>
+        <v>112.82</v>
       </c>
       <c r="B314" t="n">
-        <v>25480</v>
+        <v>23594</v>
       </c>
       <c r="C314" t="n">
-        <v>95.03</v>
+        <v>101.9</v>
       </c>
       <c r="D314" t="n">
-        <v>18434</v>
+        <v>29136</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>91.27</v>
+        <v>112.82</v>
       </c>
       <c r="B315" t="n">
-        <v>25395</v>
+        <v>23187</v>
       </c>
       <c r="C315" t="n">
-        <v>94.25</v>
+        <v>95.41</v>
       </c>
       <c r="D315" t="n">
-        <v>23177</v>
+        <v>23403</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>96.33</v>
+        <v>112.89</v>
       </c>
       <c r="B316" t="n">
-        <v>37394</v>
+        <v>21672</v>
       </c>
       <c r="C316" t="n">
-        <v>99.76000000000001</v>
+        <v>101.56</v>
       </c>
       <c r="D316" t="n">
-        <v>13063</v>
+        <v>12268</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>102.3</v>
+        <v>113.39</v>
       </c>
       <c r="B317" t="n">
-        <v>46283</v>
+        <v>22278</v>
       </c>
       <c r="C317" t="n">
-        <v>101.24</v>
+        <v>127.61</v>
       </c>
       <c r="D317" t="n">
-        <v>19940</v>
+        <v>27686</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>108.53</v>
+        <v>115.17</v>
       </c>
       <c r="B318" t="n">
-        <v>37572</v>
+        <v>20474</v>
       </c>
       <c r="C318" t="n">
-        <v>112.2</v>
+        <v>135.15</v>
       </c>
       <c r="D318" t="n">
-        <v>23190</v>
+        <v>17631</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>103.92</v>
+        <v>115.97</v>
       </c>
       <c r="B319" t="n">
-        <v>47652</v>
+        <v>20191</v>
       </c>
       <c r="C319" t="n">
-        <v>100.9</v>
+        <v>130.15</v>
       </c>
       <c r="D319" t="n">
-        <v>11322</v>
+        <v>22614</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>110.01</v>
+        <v>116.88</v>
       </c>
       <c r="B320" t="n">
-        <v>31964</v>
+        <v>19693</v>
       </c>
       <c r="C320" t="n">
-        <v>106.45</v>
+        <v>146.03</v>
       </c>
       <c r="D320" t="n">
-        <v>26793</v>
+        <v>26095</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>94.22</v>
+        <v>117.3</v>
       </c>
       <c r="B321" t="n">
-        <v>30402</v>
+        <v>21019</v>
       </c>
       <c r="C321" t="n">
-        <v>96.42</v>
+        <v>131.44</v>
       </c>
       <c r="D321" t="n">
-        <v>14652</v>
+        <v>27388</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>93.36</v>
+        <v>117.46</v>
       </c>
       <c r="B322" t="n">
-        <v>28250</v>
+        <v>20469</v>
       </c>
       <c r="C322" t="n">
-        <v>92.20999999999999</v>
+        <v>141.41</v>
       </c>
       <c r="D322" t="n">
-        <v>19403</v>
+        <v>27958</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>106.9</v>
+        <v>117.71</v>
       </c>
       <c r="B323" t="n">
-        <v>43221</v>
+        <v>19505</v>
       </c>
       <c r="C323" t="n">
-        <v>103.27</v>
+        <v>126.05</v>
       </c>
       <c r="D323" t="n">
-        <v>21596</v>
+        <v>17460</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>95.65000000000001</v>
+        <v>117.86</v>
       </c>
       <c r="B324" t="n">
-        <v>36177</v>
+        <v>21119</v>
       </c>
       <c r="C324" t="n">
-        <v>97.88</v>
+        <v>127.68</v>
       </c>
       <c r="D324" t="n">
-        <v>21090</v>
+        <v>29935</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>101.95</v>
+        <v>118.93</v>
       </c>
       <c r="B325" t="n">
-        <v>48073</v>
+        <v>21166</v>
       </c>
       <c r="C325" t="n">
-        <v>100.91</v>
+        <v>111.17</v>
       </c>
       <c r="D325" t="n">
-        <v>28254</v>
+        <v>11132</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>98.89</v>
+        <v>119.03</v>
       </c>
       <c r="B326" t="n">
-        <v>43683</v>
+        <v>19840</v>
       </c>
       <c r="C326" t="n">
-        <v>100.5</v>
+        <v>111.79</v>
       </c>
       <c r="D326" t="n">
-        <v>28435</v>
+        <v>13770</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>92.36</v>
+        <v>119.41</v>
       </c>
       <c r="B327" t="n">
-        <v>26438</v>
+        <v>19238</v>
       </c>
       <c r="C327" t="n">
-        <v>94.2</v>
+        <v>143.58</v>
       </c>
       <c r="D327" t="n">
-        <v>13877</v>
+        <v>13933</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>96.84999999999999</v>
+        <v>119.63</v>
       </c>
       <c r="B328" t="n">
-        <v>41616</v>
+        <v>19797</v>
       </c>
       <c r="C328" t="n">
-        <v>93.98</v>
+        <v>124.71</v>
       </c>
       <c r="D328" t="n">
-        <v>23133</v>
+        <v>24272</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>101.05</v>
+        <v>120.1</v>
       </c>
       <c r="B329" t="n">
-        <v>44891</v>
+        <v>19543</v>
       </c>
       <c r="C329" t="n">
-        <v>103.71</v>
+        <v>115.33</v>
       </c>
       <c r="D329" t="n">
-        <v>26343</v>
+        <v>17689</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>97.59</v>
+        <v>120.22</v>
       </c>
       <c r="B330" t="n">
-        <v>39236</v>
+        <v>20604</v>
       </c>
       <c r="C330" t="n">
-        <v>96.29000000000001</v>
+        <v>135.66</v>
       </c>
       <c r="D330" t="n">
-        <v>16742</v>
+        <v>15237</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>2.72</v>
+        <v>120.24</v>
       </c>
       <c r="B331" t="n">
-        <v>27314</v>
+        <v>19550</v>
       </c>
       <c r="C331" t="n">
-        <v>1.82</v>
+        <v>123.56</v>
       </c>
       <c r="D331" t="n">
-        <v>10238</v>
+        <v>10216</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>112.4</v>
+        <v>120.29</v>
       </c>
       <c r="B332" t="n">
-        <v>27319</v>
+        <v>19325</v>
       </c>
       <c r="C332" t="n">
-        <v>114.94</v>
+        <v>127.4</v>
       </c>
       <c r="D332" t="n">
-        <v>16700</v>
+        <v>17073</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>91.83</v>
+        <v>121.02</v>
       </c>
       <c r="B333" t="n">
-        <v>26845</v>
+        <v>21073</v>
       </c>
       <c r="C333" t="n">
-        <v>95.81999999999999</v>
+        <v>111.45</v>
       </c>
       <c r="D333" t="n">
-        <v>10437</v>
+        <v>16991</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>95.06</v>
+        <v>121.43</v>
       </c>
       <c r="B334" t="n">
-        <v>34599</v>
+        <v>19106</v>
       </c>
       <c r="C334" t="n">
-        <v>93.45</v>
+        <v>116.37</v>
       </c>
       <c r="D334" t="n">
-        <v>14403</v>
+        <v>17507</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>29.5</v>
+        <v>121.82</v>
       </c>
       <c r="B335" t="n">
-        <v>23645</v>
+        <v>19189</v>
       </c>
       <c r="C335" t="n">
-        <v>28.3</v>
+        <v>119.03</v>
       </c>
       <c r="D335" t="n">
-        <v>23067</v>
+        <v>11478</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>101.33</v>
+        <v>121.93</v>
       </c>
       <c r="B336" t="n">
-        <v>45638</v>
+        <v>18008</v>
       </c>
       <c r="C336" t="n">
-        <v>99.39</v>
+        <v>143.91</v>
       </c>
       <c r="D336" t="n">
-        <v>12453</v>
+        <v>11297</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>111.57</v>
+        <v>122.24</v>
       </c>
       <c r="B337" t="n">
-        <v>28098</v>
+        <v>19161</v>
       </c>
       <c r="C337" t="n">
-        <v>108.69</v>
+        <v>116.66</v>
       </c>
       <c r="D337" t="n">
-        <v>27085</v>
+        <v>12125</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>108.45</v>
+        <v>122.67</v>
       </c>
       <c r="B338" t="n">
-        <v>38351</v>
+        <v>18722</v>
       </c>
       <c r="C338" t="n">
-        <v>107.32</v>
+        <v>152.99</v>
       </c>
       <c r="D338" t="n">
-        <v>17931</v>
+        <v>17622</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>27.82</v>
+        <v>122.82</v>
       </c>
       <c r="B339" t="n">
-        <v>23582</v>
+        <v>20576</v>
       </c>
       <c r="C339" t="n">
-        <v>27.39</v>
+        <v>122.39</v>
       </c>
       <c r="D339" t="n">
-        <v>15555</v>
+        <v>17131</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>114.04</v>
+        <v>122.88</v>
       </c>
       <c r="B340" t="n">
-        <v>27008</v>
+        <v>19911</v>
       </c>
       <c r="C340" t="n">
-        <v>116.61</v>
+        <v>113.99</v>
       </c>
       <c r="D340" t="n">
-        <v>22118</v>
+        <v>11402</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>110.31</v>
+        <v>122.98</v>
       </c>
       <c r="B341" t="n">
-        <v>33173</v>
+        <v>19288</v>
       </c>
       <c r="C341" t="n">
-        <v>111.99</v>
+        <v>98.89</v>
       </c>
       <c r="D341" t="n">
-        <v>14093</v>
+        <v>22107</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>114.92</v>
+        <v>123.47</v>
       </c>
       <c r="B342" t="n">
-        <v>22588</v>
+        <v>20099</v>
       </c>
       <c r="C342" t="n">
-        <v>115.88</v>
+        <v>101.08</v>
       </c>
       <c r="D342" t="n">
-        <v>12295</v>
+        <v>27952</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>97.65000000000001</v>
+        <v>123.66</v>
       </c>
       <c r="B343" t="n">
-        <v>42917</v>
+        <v>19548</v>
       </c>
       <c r="C343" t="n">
-        <v>94.66</v>
+        <v>136.86</v>
       </c>
       <c r="D343" t="n">
-        <v>18566</v>
+        <v>21150</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>113.73</v>
+        <v>124.01</v>
       </c>
       <c r="B344" t="n">
-        <v>23955</v>
+        <v>18769</v>
       </c>
       <c r="C344" t="n">
-        <v>112.72</v>
+        <v>144.98</v>
       </c>
       <c r="D344" t="n">
-        <v>14659</v>
+        <v>13972</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>94.02</v>
+        <v>124.01</v>
       </c>
       <c r="B345" t="n">
-        <v>30034</v>
+        <v>20312</v>
       </c>
       <c r="C345" t="n">
-        <v>92.87</v>
+        <v>109.18</v>
       </c>
       <c r="D345" t="n">
-        <v>10807</v>
+        <v>16783</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>113.53</v>
+        <v>124.85</v>
       </c>
       <c r="B346" t="n">
-        <v>23024</v>
+        <v>19672</v>
       </c>
       <c r="C346" t="n">
-        <v>111.52</v>
+        <v>112.04</v>
       </c>
       <c r="D346" t="n">
-        <v>11679</v>
+        <v>29830</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>94.84999999999999</v>
+        <v>125.45</v>
       </c>
       <c r="B347" t="n">
-        <v>34052</v>
+        <v>20426</v>
       </c>
       <c r="C347" t="n">
-        <v>99.2</v>
+        <v>137.76</v>
       </c>
       <c r="D347" t="n">
-        <v>23208</v>
+        <v>15017</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>97.34999999999999</v>
+        <v>125.93</v>
       </c>
       <c r="B348" t="n">
-        <v>40466</v>
+        <v>20102</v>
       </c>
       <c r="C348" t="n">
-        <v>98.72</v>
+        <v>106.08</v>
       </c>
       <c r="D348" t="n">
-        <v>27925</v>
+        <v>19697</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>109.86</v>
+        <v>126.31</v>
       </c>
       <c r="B349" t="n">
-        <v>34064</v>
+        <v>17392</v>
       </c>
       <c r="C349" t="n">
-        <v>106.19</v>
+        <v>133.55</v>
       </c>
       <c r="D349" t="n">
-        <v>26940</v>
+        <v>20441</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>97.92</v>
+        <v>126.43</v>
       </c>
       <c r="B350" t="n">
-        <v>44421</v>
+        <v>18894</v>
       </c>
       <c r="C350" t="n">
-        <v>95.28</v>
+        <v>139.84</v>
       </c>
       <c r="D350" t="n">
-        <v>21623</v>
+        <v>14931</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>106.13</v>
+        <v>126.58</v>
       </c>
       <c r="B351" t="n">
-        <v>47512</v>
+        <v>20601</v>
       </c>
       <c r="C351" t="n">
-        <v>105.45</v>
+        <v>127.56</v>
       </c>
       <c r="D351" t="n">
-        <v>16605</v>
+        <v>29645</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>110.05</v>
+        <v>126.64</v>
       </c>
       <c r="B352" t="n">
-        <v>33781</v>
+        <v>18539</v>
       </c>
       <c r="C352" t="n">
-        <v>112.36</v>
+        <v>126.24</v>
       </c>
       <c r="D352" t="n">
-        <v>23365</v>
+        <v>21224</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>96.48</v>
+        <v>127.99</v>
       </c>
       <c r="B353" t="n">
-        <v>38223</v>
+        <v>19673</v>
       </c>
       <c r="C353" t="n">
-        <v>96.2</v>
+        <v>116.94</v>
       </c>
       <c r="D353" t="n">
-        <v>12931</v>
+        <v>29183</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>99.3</v>
+        <v>128.16</v>
       </c>
       <c r="B354" t="n">
-        <v>44533</v>
+        <v>18077</v>
       </c>
       <c r="C354" t="n">
-        <v>99.68000000000001</v>
+        <v>139.07</v>
       </c>
       <c r="D354" t="n">
-        <v>17994</v>
+        <v>14015</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>136.29</v>
+        <v>128.71</v>
       </c>
       <c r="B355" t="n">
-        <v>19147</v>
+        <v>19450</v>
       </c>
       <c r="C355" t="n">
-        <v>140.07</v>
+        <v>107.3</v>
       </c>
       <c r="D355" t="n">
-        <v>15417</v>
+        <v>21135</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>101.67</v>
+        <v>129.18</v>
       </c>
       <c r="B356" t="n">
-        <v>44522</v>
+        <v>19310</v>
       </c>
       <c r="C356" t="n">
-        <v>101.33</v>
+        <v>135.81</v>
       </c>
       <c r="D356" t="n">
-        <v>22353</v>
+        <v>27475</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>38.61</v>
+        <v>129.39</v>
       </c>
       <c r="B357" t="n">
-        <v>24398</v>
+        <v>20121</v>
       </c>
       <c r="C357" t="n">
-        <v>38.87</v>
+        <v>130.23</v>
       </c>
       <c r="D357" t="n">
-        <v>28974</v>
+        <v>29856</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>97.73999999999999</v>
+        <v>129.39</v>
       </c>
       <c r="B358" t="n">
-        <v>40558</v>
+        <v>15654</v>
       </c>
       <c r="C358" t="n">
-        <v>95.88</v>
+        <v>161.6</v>
       </c>
       <c r="D358" t="n">
-        <v>25489</v>
+        <v>20967</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>113.48</v>
+        <v>129.54</v>
       </c>
       <c r="B359" t="n">
-        <v>20591</v>
+        <v>18654</v>
       </c>
       <c r="C359" t="n">
-        <v>114.09</v>
+        <v>117.26</v>
       </c>
       <c r="D359" t="n">
-        <v>20914</v>
+        <v>29707</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>98.09</v>
+        <v>129.6</v>
       </c>
       <c r="B360" t="n">
-        <v>41158</v>
+        <v>19887</v>
       </c>
       <c r="C360" t="n">
-        <v>94.47</v>
+        <v>133.11</v>
       </c>
       <c r="D360" t="n">
-        <v>18816</v>
+        <v>13924</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>108.76</v>
+        <v>130.26</v>
       </c>
       <c r="B361" t="n">
-        <v>36689</v>
+        <v>19614</v>
       </c>
       <c r="C361" t="n">
-        <v>107.96</v>
+        <v>124.71</v>
       </c>
       <c r="D361" t="n">
-        <v>12431</v>
+        <v>11436</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>164.95</v>
+        <v>130.59</v>
       </c>
       <c r="B362" t="n">
-        <v>23766</v>
+        <v>21384</v>
       </c>
       <c r="C362" t="n">
-        <v>161.42</v>
+        <v>110.09</v>
       </c>
       <c r="D362" t="n">
-        <v>28415</v>
+        <v>26667</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>98.12</v>
+        <v>131.38</v>
       </c>
       <c r="B363" t="n">
-        <v>40383</v>
+        <v>18917</v>
       </c>
       <c r="C363" t="n">
-        <v>96.58</v>
+        <v>150.38</v>
       </c>
       <c r="D363" t="n">
-        <v>22870</v>
+        <v>27498</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>92.2</v>
+        <v>131.46</v>
       </c>
       <c r="B364" t="n">
-        <v>25154</v>
+        <v>18290</v>
       </c>
       <c r="C364" t="n">
-        <v>95.87</v>
+        <v>143.53</v>
       </c>
       <c r="D364" t="n">
-        <v>27398</v>
+        <v>23844</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>100.49</v>
+        <v>132.08</v>
       </c>
       <c r="B365" t="n">
-        <v>43911</v>
+        <v>18495</v>
       </c>
       <c r="C365" t="n">
-        <v>100.38</v>
+        <v>122.64</v>
       </c>
       <c r="D365" t="n">
-        <v>29697</v>
+        <v>10430</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>150.76</v>
+        <v>132.16</v>
       </c>
       <c r="B366" t="n">
-        <v>21621</v>
+        <v>17651</v>
       </c>
       <c r="C366" t="n">
-        <v>155.7</v>
+        <v>139.9</v>
       </c>
       <c r="D366" t="n">
-        <v>21885</v>
+        <v>22450</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>112.53</v>
+        <v>132.91</v>
       </c>
       <c r="B367" t="n">
-        <v>24392</v>
+        <v>19365</v>
       </c>
       <c r="C367" t="n">
-        <v>109.25</v>
+        <v>139.18</v>
       </c>
       <c r="D367" t="n">
-        <v>25057</v>
+        <v>18625</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
-        <v>100.64</v>
+        <v>133.58</v>
       </c>
       <c r="B368" t="n">
-        <v>45219</v>
+        <v>18600</v>
       </c>
       <c r="C368" t="n">
-        <v>99.25</v>
+        <v>163.81</v>
       </c>
       <c r="D368" t="n">
-        <v>26798</v>
+        <v>28381</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
-        <v>111.99</v>
+        <v>134.29</v>
       </c>
       <c r="B369" t="n">
-        <v>26246</v>
+        <v>19437</v>
       </c>
       <c r="C369" t="n">
-        <v>108.27</v>
+        <v>153.38</v>
       </c>
       <c r="D369" t="n">
-        <v>15777</v>
+        <v>15297</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>94.81999999999999</v>
+        <v>134.48</v>
       </c>
       <c r="B370" t="n">
-        <v>32996</v>
+        <v>21038</v>
       </c>
       <c r="C370" t="n">
-        <v>92.65000000000001</v>
+        <v>107.75</v>
       </c>
       <c r="D370" t="n">
-        <v>26537</v>
+        <v>18187</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
-        <v>135.76</v>
+        <v>135.13</v>
       </c>
       <c r="B371" t="n">
-        <v>22467</v>
+        <v>23277</v>
       </c>
       <c r="C371" t="n">
-        <v>132.03</v>
+        <v>140.13</v>
       </c>
       <c r="D371" t="n">
-        <v>23761</v>
+        <v>16594</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>15.07</v>
+        <v>135.63</v>
       </c>
       <c r="B372" t="n">
-        <v>21781</v>
+        <v>22132</v>
       </c>
       <c r="C372" t="n">
-        <v>14.26</v>
+        <v>149.52</v>
       </c>
       <c r="D372" t="n">
-        <v>29807</v>
+        <v>17256</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>90.86</v>
+        <v>136.45</v>
       </c>
       <c r="B373" t="n">
-        <v>24592</v>
+        <v>16362</v>
       </c>
       <c r="C373" t="n">
-        <v>87.81999999999999</v>
+        <v>146.9</v>
       </c>
       <c r="D373" t="n">
-        <v>19287</v>
+        <v>26025</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
-        <v>108.92</v>
+        <v>137.29</v>
       </c>
       <c r="B374" t="n">
-        <v>33690</v>
+        <v>20625</v>
       </c>
       <c r="C374" t="n">
-        <v>108.77</v>
+        <v>127.18</v>
       </c>
       <c r="D374" t="n">
-        <v>19374</v>
+        <v>27835</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
-        <v>146.53</v>
+        <v>137.44</v>
       </c>
       <c r="B375" t="n">
-        <v>22856</v>
+        <v>18624</v>
       </c>
       <c r="C375" t="n">
-        <v>144.13</v>
+        <v>135.17</v>
       </c>
       <c r="D375" t="n">
-        <v>25823</v>
+        <v>29553</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
-        <v>91.69</v>
+        <v>138.21</v>
       </c>
       <c r="B376" t="n">
-        <v>25659</v>
+        <v>17247</v>
       </c>
       <c r="C376" t="n">
-        <v>93.3</v>
+        <v>152.08</v>
       </c>
       <c r="D376" t="n">
-        <v>28955</v>
+        <v>13237</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
-        <v>102.74</v>
+        <v>139.45</v>
       </c>
       <c r="B377" t="n">
-        <v>44132</v>
+        <v>21181</v>
       </c>
       <c r="C377" t="n">
-        <v>104.66</v>
+        <v>154.88</v>
       </c>
       <c r="D377" t="n">
-        <v>23257</v>
+        <v>23080</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
-        <v>107.66</v>
+        <v>139.56</v>
       </c>
       <c r="B378" t="n">
-        <v>38951</v>
+        <v>19456</v>
       </c>
       <c r="C378" t="n">
-        <v>107.05</v>
+        <v>169.46</v>
       </c>
       <c r="D378" t="n">
-        <v>28876</v>
+        <v>28330</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
-        <v>11.59</v>
+        <v>140.3</v>
       </c>
       <c r="B379" t="n">
-        <v>23614</v>
+        <v>20008</v>
       </c>
       <c r="C379" t="n">
-        <v>11.71</v>
+        <v>125.5</v>
       </c>
       <c r="D379" t="n">
-        <v>26437</v>
+        <v>26294</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
-        <v>169.51</v>
+        <v>140.47</v>
       </c>
       <c r="B380" t="n">
-        <v>22095</v>
+        <v>19525</v>
       </c>
       <c r="C380" t="n">
-        <v>169.3</v>
+        <v>159.92</v>
       </c>
       <c r="D380" t="n">
-        <v>24013</v>
+        <v>29686</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>106.42</v>
+        <v>140.54</v>
       </c>
       <c r="B381" t="n">
-        <v>43765</v>
+        <v>18513</v>
       </c>
       <c r="C381" t="n">
-        <v>105.53</v>
+        <v>143.77</v>
       </c>
       <c r="D381" t="n">
-        <v>16960</v>
+        <v>19261</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
-        <v>68.81</v>
+        <v>140.55</v>
       </c>
       <c r="B382" t="n">
-        <v>24244</v>
+        <v>18426</v>
       </c>
       <c r="C382" t="n">
-        <v>69.06</v>
+        <v>163.85</v>
       </c>
       <c r="D382" t="n">
-        <v>16515</v>
+        <v>26598</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>98.95</v>
+        <v>140.68</v>
       </c>
       <c r="B383" t="n">
-        <v>43627</v>
+        <v>17790</v>
       </c>
       <c r="C383" t="n">
-        <v>100.88</v>
+        <v>152.16</v>
       </c>
       <c r="D383" t="n">
-        <v>24341</v>
+        <v>13060</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>110.67</v>
+        <v>140.77</v>
       </c>
       <c r="B384" t="n">
-        <v>29146</v>
+        <v>18087</v>
       </c>
       <c r="C384" t="n">
-        <v>112.22</v>
+        <v>134.76</v>
       </c>
       <c r="D384" t="n">
-        <v>20145</v>
+        <v>11448</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>106.63</v>
+        <v>140.92</v>
       </c>
       <c r="B385" t="n">
-        <v>41290</v>
+        <v>20099</v>
       </c>
       <c r="C385" t="n">
-        <v>110.91</v>
+        <v>110.87</v>
       </c>
       <c r="D385" t="n">
-        <v>23346</v>
+        <v>22735</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
-        <v>110.15</v>
+        <v>141.03</v>
       </c>
       <c r="B386" t="n">
-        <v>31069</v>
+        <v>19806</v>
       </c>
       <c r="C386" t="n">
-        <v>113</v>
+        <v>147.49</v>
       </c>
       <c r="D386" t="n">
-        <v>25517</v>
+        <v>22180</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>71.03</v>
+        <v>141.15</v>
       </c>
       <c r="B387" t="n">
-        <v>23834</v>
+        <v>23318</v>
       </c>
       <c r="C387" t="n">
-        <v>73.26000000000001</v>
+        <v>162.54</v>
       </c>
       <c r="D387" t="n">
-        <v>16385</v>
+        <v>18701</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>128.51</v>
+        <v>141.79</v>
       </c>
       <c r="B388" t="n">
-        <v>23550</v>
+        <v>18809</v>
       </c>
       <c r="C388" t="n">
-        <v>123.75</v>
+        <v>117.91</v>
       </c>
       <c r="D388" t="n">
-        <v>20052</v>
+        <v>22870</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>143.72</v>
+        <v>141.95</v>
       </c>
       <c r="B389" t="n">
-        <v>23077</v>
+        <v>19422</v>
       </c>
       <c r="C389" t="n">
-        <v>139.7</v>
+        <v>126.85</v>
       </c>
       <c r="D389" t="n">
-        <v>13442</v>
+        <v>19912</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
-        <v>174.34</v>
+        <v>142.06</v>
       </c>
       <c r="B390" t="n">
-        <v>23511</v>
+        <v>19282</v>
       </c>
       <c r="C390" t="n">
-        <v>178.3</v>
+        <v>126.65</v>
       </c>
       <c r="D390" t="n">
-        <v>10477</v>
+        <v>13887</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
-        <v>114.81</v>
+        <v>142.29</v>
       </c>
       <c r="B391" t="n">
-        <v>24468</v>
+        <v>21054</v>
       </c>
       <c r="C391" t="n">
-        <v>111.26</v>
+        <v>158.47</v>
       </c>
       <c r="D391" t="n">
-        <v>27345</v>
+        <v>18039</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
-        <v>92.53</v>
+        <v>142.74</v>
       </c>
       <c r="B392" t="n">
-        <v>25665</v>
+        <v>18346</v>
       </c>
       <c r="C392" t="n">
-        <v>95.70999999999999</v>
+        <v>143.9</v>
       </c>
       <c r="D392" t="n">
-        <v>19441</v>
+        <v>19750</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
-        <v>92.01000000000001</v>
+        <v>142.82</v>
       </c>
       <c r="B393" t="n">
-        <v>27350</v>
+        <v>21447</v>
       </c>
       <c r="C393" t="n">
-        <v>94.09</v>
+        <v>161.48</v>
       </c>
       <c r="D393" t="n">
-        <v>27659</v>
+        <v>11809</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
-        <v>112.8</v>
+        <v>142.93</v>
       </c>
       <c r="B394" t="n">
-        <v>26211</v>
+        <v>21278</v>
       </c>
       <c r="C394" t="n">
-        <v>109.55</v>
+        <v>155.19</v>
       </c>
       <c r="D394" t="n">
-        <v>13446</v>
+        <v>24117</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
-        <v>108.64</v>
+        <v>142.97</v>
       </c>
       <c r="B395" t="n">
-        <v>35251</v>
+        <v>20236</v>
       </c>
       <c r="C395" t="n">
-        <v>109.5</v>
+        <v>157.9</v>
       </c>
       <c r="D395" t="n">
-        <v>14763</v>
+        <v>21374</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
-        <v>105.1</v>
+        <v>143.15</v>
       </c>
       <c r="B396" t="n">
-        <v>46577</v>
+        <v>19389</v>
       </c>
       <c r="C396" t="n">
-        <v>104.9</v>
+        <v>122.48</v>
       </c>
       <c r="D396" t="n">
-        <v>22023</v>
+        <v>21896</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
-        <v>104.04</v>
+        <v>143.93</v>
       </c>
       <c r="B397" t="n">
-        <v>48383</v>
+        <v>20307</v>
       </c>
       <c r="C397" t="n">
-        <v>104.15</v>
+        <v>145.17</v>
       </c>
       <c r="D397" t="n">
-        <v>20981</v>
+        <v>28944</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
-        <v>95.73999999999999</v>
+        <v>144.22</v>
       </c>
       <c r="B398" t="n">
-        <v>35272</v>
+        <v>20754</v>
       </c>
       <c r="C398" t="n">
-        <v>96.67</v>
+        <v>161.54</v>
       </c>
       <c r="D398" t="n">
-        <v>17587</v>
+        <v>12862</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
-        <v>106.23</v>
+        <v>144.38</v>
       </c>
       <c r="B399" t="n">
-        <v>43600</v>
+        <v>18540</v>
       </c>
       <c r="C399" t="n">
-        <v>104.8</v>
+        <v>140.35</v>
       </c>
       <c r="D399" t="n">
-        <v>25209</v>
+        <v>24086</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
-        <v>113.47</v>
+        <v>144.44</v>
       </c>
       <c r="B400" t="n">
-        <v>25664</v>
+        <v>20251</v>
       </c>
       <c r="C400" t="n">
-        <v>112.74</v>
+        <v>137.41</v>
       </c>
       <c r="D400" t="n">
-        <v>10830</v>
+        <v>12296</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
-        <v>109.6</v>
+        <v>144.72</v>
       </c>
       <c r="B401" t="n">
-        <v>33501</v>
+        <v>18659</v>
       </c>
       <c r="C401" t="n">
-        <v>112.75</v>
+        <v>165.59</v>
       </c>
       <c r="D401" t="n">
-        <v>19761</v>
+        <v>16401</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
-        <v>104.29</v>
+        <v>145.09</v>
       </c>
       <c r="B402" t="n">
-        <v>47835</v>
+        <v>19762</v>
       </c>
       <c r="C402" t="n">
-        <v>104.43</v>
+        <v>123.81</v>
       </c>
       <c r="D402" t="n">
-        <v>14812</v>
+        <v>23259</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
-        <v>99.14</v>
+        <v>146.23</v>
       </c>
       <c r="B403" t="n">
-        <v>41644</v>
+        <v>22065</v>
       </c>
       <c r="C403" t="n">
-        <v>95.55</v>
+        <v>130.7</v>
       </c>
       <c r="D403" t="n">
-        <v>16393</v>
+        <v>24785</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
-        <v>100.23</v>
+        <v>146.51</v>
       </c>
       <c r="B404" t="n">
-        <v>44083</v>
+        <v>20729</v>
       </c>
       <c r="C404" t="n">
-        <v>102.89</v>
+        <v>161.96</v>
       </c>
       <c r="D404" t="n">
-        <v>23170</v>
+        <v>26268</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
-        <v>98.01000000000001</v>
+        <v>147.07</v>
       </c>
       <c r="B405" t="n">
-        <v>41885</v>
+        <v>20164</v>
       </c>
       <c r="C405" t="n">
-        <v>96.12</v>
+        <v>134.87</v>
       </c>
       <c r="D405" t="n">
-        <v>18961</v>
+        <v>29040</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
-        <v>63.47</v>
+        <v>147.5</v>
       </c>
       <c r="B406" t="n">
-        <v>25710</v>
+        <v>22103</v>
       </c>
       <c r="C406" t="n">
-        <v>64.88</v>
+        <v>169.99</v>
       </c>
       <c r="D406" t="n">
-        <v>24624</v>
+        <v>21173</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
-        <v>107.28</v>
+        <v>148.29</v>
       </c>
       <c r="B407" t="n">
-        <v>42781</v>
+        <v>21366</v>
       </c>
       <c r="C407" t="n">
-        <v>108.56</v>
+        <v>165.58</v>
       </c>
       <c r="D407" t="n">
-        <v>19041</v>
+        <v>29157</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
-        <v>106.45</v>
+        <v>148.41</v>
       </c>
       <c r="B408" t="n">
-        <v>41122</v>
+        <v>19261</v>
       </c>
       <c r="C408" t="n">
-        <v>110.18</v>
+        <v>132.48</v>
       </c>
       <c r="D408" t="n">
-        <v>11861</v>
+        <v>21469</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
-        <v>95.31</v>
+        <v>148.77</v>
       </c>
       <c r="B409" t="n">
-        <v>33129</v>
+        <v>21374</v>
       </c>
       <c r="C409" t="n">
-        <v>91.81999999999999</v>
+        <v>139.01</v>
       </c>
       <c r="D409" t="n">
-        <v>16154</v>
+        <v>26035</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
-        <v>112.19</v>
+        <v>148.82</v>
       </c>
       <c r="B410" t="n">
-        <v>25113</v>
+        <v>22801</v>
       </c>
       <c r="C410" t="n">
-        <v>113.97</v>
+        <v>153.31</v>
       </c>
       <c r="D410" t="n">
-        <v>14347</v>
+        <v>24171</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
-        <v>104.23</v>
+        <v>148.96</v>
       </c>
       <c r="B411" t="n">
-        <v>45822</v>
+        <v>26538</v>
       </c>
       <c r="C411" t="n">
-        <v>102.18</v>
+        <v>148.21</v>
       </c>
       <c r="D411" t="n">
-        <v>15166</v>
+        <v>11168</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
-        <v>105.9</v>
+        <v>149.12</v>
       </c>
       <c r="B412" t="n">
-        <v>45336</v>
+        <v>24004</v>
       </c>
       <c r="C412" t="n">
-        <v>106.07</v>
+        <v>128.36</v>
       </c>
       <c r="D412" t="n">
-        <v>26654</v>
+        <v>20379</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
-        <v>113.68</v>
+        <v>149.24</v>
       </c>
       <c r="B413" t="n">
-        <v>22274</v>
+        <v>23390</v>
       </c>
       <c r="C413" t="n">
-        <v>114.91</v>
+        <v>155.07</v>
       </c>
       <c r="D413" t="n">
-        <v>10853</v>
+        <v>13306</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
-        <v>96.37</v>
+        <v>149.39</v>
       </c>
       <c r="B414" t="n">
-        <v>36609</v>
+        <v>22199</v>
       </c>
       <c r="C414" t="n">
-        <v>96.72</v>
+        <v>121</v>
       </c>
       <c r="D414" t="n">
-        <v>19095</v>
+        <v>14418</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
-        <v>10.88</v>
+        <v>149.4</v>
       </c>
       <c r="B415" t="n">
-        <v>22218</v>
+        <v>22282</v>
       </c>
       <c r="C415" t="n">
-        <v>11.48</v>
+        <v>179.83</v>
       </c>
       <c r="D415" t="n">
-        <v>10979</v>
+        <v>12307</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
-        <v>94.05</v>
+        <v>149.8</v>
       </c>
       <c r="B416" t="n">
-        <v>31888</v>
+        <v>23284</v>
       </c>
       <c r="C416" t="n">
-        <v>95.59</v>
+        <v>175.14</v>
       </c>
       <c r="D416" t="n">
-        <v>21024</v>
+        <v>17948</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
-        <v>7.31</v>
+        <v>149.96</v>
       </c>
       <c r="B417" t="n">
-        <v>21920</v>
+        <v>20834</v>
       </c>
       <c r="C417" t="n">
-        <v>8.74</v>
+        <v>138.55</v>
       </c>
       <c r="D417" t="n">
-        <v>29694</v>
+        <v>22421</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
-        <v>108.27</v>
+        <v>151.31</v>
       </c>
       <c r="B418" t="n">
-        <v>37972</v>
+        <v>24300</v>
       </c>
       <c r="C418" t="n">
-        <v>104.44</v>
+        <v>139.32</v>
       </c>
       <c r="D418" t="n">
-        <v>20385</v>
+        <v>14915</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="n">
-        <v>111.23</v>
+        <v>151.74</v>
       </c>
       <c r="B419" t="n">
-        <v>28638</v>
+        <v>24559</v>
       </c>
       <c r="C419" t="n">
-        <v>111.79</v>
+        <v>175.75</v>
       </c>
       <c r="D419" t="n">
-        <v>10858</v>
+        <v>28486</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="n">
-        <v>107.77</v>
+        <v>152.15</v>
       </c>
       <c r="B420" t="n">
-        <v>41358</v>
+        <v>24378</v>
       </c>
       <c r="C420" t="n">
-        <v>103.87</v>
+        <v>180</v>
       </c>
       <c r="D420" t="n">
-        <v>15501</v>
+        <v>21852</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="n">
-        <v>111.71</v>
+        <v>152.25</v>
       </c>
       <c r="B421" t="n">
-        <v>29685</v>
+        <v>25430</v>
       </c>
       <c r="C421" t="n">
-        <v>111.07</v>
+        <v>119.45</v>
       </c>
       <c r="D421" t="n">
-        <v>11054</v>
+        <v>10585</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="n">
-        <v>72.68000000000001</v>
+        <v>152.31</v>
       </c>
       <c r="B422" t="n">
-        <v>24562</v>
+        <v>27245</v>
       </c>
       <c r="C422" t="n">
-        <v>75.37</v>
+        <v>178.21</v>
       </c>
       <c r="D422" t="n">
-        <v>28893</v>
+        <v>13798</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
-        <v>20.54</v>
+        <v>152.5</v>
       </c>
       <c r="B423" t="n">
-        <v>24487</v>
+        <v>25793</v>
       </c>
       <c r="C423" t="n">
-        <v>20.59</v>
+        <v>139.48</v>
       </c>
       <c r="D423" t="n">
-        <v>21518</v>
+        <v>21660</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="n">
-        <v>107.4</v>
+        <v>152.57</v>
       </c>
       <c r="B424" t="n">
-        <v>40294</v>
+        <v>24120</v>
       </c>
       <c r="C424" t="n">
-        <v>108.05</v>
+        <v>180</v>
       </c>
       <c r="D424" t="n">
-        <v>11610</v>
+        <v>14888</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="n">
-        <v>107.85</v>
+        <v>152.64</v>
       </c>
       <c r="B425" t="n">
-        <v>39088</v>
+        <v>25061</v>
       </c>
       <c r="C425" t="n">
-        <v>104.03</v>
+        <v>139.53</v>
       </c>
       <c r="D425" t="n">
-        <v>13694</v>
+        <v>16999</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="n">
-        <v>106.41</v>
+        <v>152.85</v>
       </c>
       <c r="B426" t="n">
-        <v>41719</v>
+        <v>27003</v>
       </c>
       <c r="C426" t="n">
-        <v>102.47</v>
+        <v>158.49</v>
       </c>
       <c r="D426" t="n">
-        <v>13544</v>
+        <v>26159</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="n">
-        <v>91.48</v>
+        <v>152.89</v>
       </c>
       <c r="B427" t="n">
-        <v>24842</v>
+        <v>24439</v>
       </c>
       <c r="C427" t="n">
-        <v>88.3</v>
+        <v>161.62</v>
       </c>
       <c r="D427" t="n">
-        <v>21652</v>
+        <v>12980</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="n">
-        <v>103.34</v>
+        <v>152.92</v>
       </c>
       <c r="B428" t="n">
-        <v>47903</v>
+        <v>25006</v>
       </c>
       <c r="C428" t="n">
-        <v>103.79</v>
+        <v>169.96</v>
       </c>
       <c r="D428" t="n">
-        <v>20936</v>
+        <v>29183</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="n">
-        <v>110.81</v>
+        <v>153.21</v>
       </c>
       <c r="B429" t="n">
-        <v>27791</v>
+        <v>27348</v>
       </c>
       <c r="C429" t="n">
-        <v>114.85</v>
+        <v>148.18</v>
       </c>
       <c r="D429" t="n">
-        <v>22009</v>
+        <v>18823</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="n">
-        <v>94.81</v>
+        <v>153.61</v>
       </c>
       <c r="B430" t="n">
-        <v>35392</v>
+        <v>24474</v>
       </c>
       <c r="C430" t="n">
-        <v>91.81</v>
+        <v>167.76</v>
       </c>
       <c r="D430" t="n">
-        <v>28799</v>
+        <v>17235</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="n">
-        <v>110.41</v>
+        <v>154.01</v>
       </c>
       <c r="B431" t="n">
-        <v>31417</v>
+        <v>26693</v>
       </c>
       <c r="C431" t="n">
-        <v>112.63</v>
+        <v>180</v>
       </c>
       <c r="D431" t="n">
-        <v>23604</v>
+        <v>22958</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="n">
-        <v>147.53</v>
+        <v>154.9</v>
       </c>
       <c r="B432" t="n">
-        <v>24457</v>
+        <v>24235</v>
       </c>
       <c r="C432" t="n">
-        <v>152.83</v>
+        <v>143.03</v>
       </c>
       <c r="D432" t="n">
-        <v>28725</v>
+        <v>25002</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="n">
-        <v>111.13</v>
+        <v>155.19</v>
       </c>
       <c r="B433" t="n">
-        <v>28254</v>
+        <v>30303</v>
       </c>
       <c r="C433" t="n">
-        <v>114.04</v>
+        <v>164.7</v>
       </c>
       <c r="D433" t="n">
-        <v>15683</v>
+        <v>10265</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="n">
-        <v>105.18</v>
+        <v>155.26</v>
       </c>
       <c r="B434" t="n">
-        <v>43973</v>
+        <v>27671</v>
       </c>
       <c r="C434" t="n">
-        <v>102.86</v>
+        <v>160.1</v>
       </c>
       <c r="D434" t="n">
-        <v>27590</v>
+        <v>26860</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="n">
-        <v>94.14</v>
+        <v>155.51</v>
       </c>
       <c r="B435" t="n">
-        <v>30480</v>
+        <v>28958</v>
       </c>
       <c r="C435" t="n">
-        <v>94.34</v>
+        <v>180</v>
       </c>
       <c r="D435" t="n">
-        <v>10047</v>
+        <v>28187</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="n">
-        <v>63.28</v>
+        <v>157.21</v>
       </c>
       <c r="B436" t="n">
-        <v>23414</v>
+        <v>31190</v>
       </c>
       <c r="C436" t="n">
-        <v>66.31</v>
+        <v>126.11</v>
       </c>
       <c r="D436" t="n">
-        <v>24788</v>
+        <v>25508</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="n">
-        <v>113.39</v>
+        <v>157.58</v>
       </c>
       <c r="B437" t="n">
-        <v>24537</v>
+        <v>29817</v>
       </c>
       <c r="C437" t="n">
-        <v>108.79</v>
+        <v>180</v>
       </c>
       <c r="D437" t="n">
-        <v>19642</v>
+        <v>10471</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="n">
-        <v>109.3</v>
+        <v>157.63</v>
       </c>
       <c r="B438" t="n">
-        <v>34492</v>
+        <v>30384</v>
       </c>
       <c r="C438" t="n">
-        <v>107.77</v>
+        <v>165.07</v>
       </c>
       <c r="D438" t="n">
-        <v>13211</v>
+        <v>21681</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="n">
-        <v>92.98999999999999</v>
+        <v>157.64</v>
       </c>
       <c r="B439" t="n">
-        <v>27796</v>
+        <v>32457</v>
       </c>
       <c r="C439" t="n">
-        <v>90.8</v>
+        <v>172.35</v>
       </c>
       <c r="D439" t="n">
-        <v>22924</v>
+        <v>14363</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="n">
-        <v>97.17</v>
+        <v>158.1</v>
       </c>
       <c r="B440" t="n">
-        <v>39260</v>
+        <v>30118</v>
       </c>
       <c r="C440" t="n">
-        <v>92.65000000000001</v>
+        <v>156.26</v>
       </c>
       <c r="D440" t="n">
-        <v>26104</v>
+        <v>22797</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="n">
-        <v>108</v>
+        <v>158.5</v>
       </c>
       <c r="B441" t="n">
-        <v>40423</v>
+        <v>31064</v>
       </c>
       <c r="C441" t="n">
-        <v>107</v>
+        <v>158.52</v>
       </c>
       <c r="D441" t="n">
-        <v>23648</v>
+        <v>11772</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="n">
-        <v>105.59</v>
+        <v>159.52</v>
       </c>
       <c r="B442" t="n">
-        <v>45615</v>
+        <v>30610</v>
       </c>
       <c r="C442" t="n">
-        <v>108.51</v>
+        <v>147.72</v>
       </c>
       <c r="D442" t="n">
-        <v>29075</v>
+        <v>28432</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="n">
-        <v>84.5</v>
+        <v>159.74</v>
       </c>
       <c r="B443" t="n">
-        <v>22199</v>
+        <v>28396</v>
       </c>
       <c r="C443" t="n">
-        <v>80.86</v>
+        <v>152.16</v>
       </c>
       <c r="D443" t="n">
-        <v>11220</v>
+        <v>22849</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="n">
-        <v>82.75</v>
+        <v>160.27</v>
       </c>
       <c r="B444" t="n">
-        <v>23856</v>
+        <v>31002</v>
       </c>
       <c r="C444" t="n">
-        <v>80.18000000000001</v>
+        <v>180</v>
       </c>
       <c r="D444" t="n">
-        <v>21202</v>
+        <v>13021</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
-        <v>103.57</v>
+        <v>160.43</v>
       </c>
       <c r="B445" t="n">
-        <v>44438</v>
+        <v>30949</v>
       </c>
       <c r="C445" t="n">
-        <v>107.67</v>
+        <v>163.18</v>
       </c>
       <c r="D445" t="n">
-        <v>19493</v>
+        <v>18791</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="n">
-        <v>90.38</v>
+        <v>160.75</v>
       </c>
       <c r="B446" t="n">
-        <v>26001</v>
+        <v>28950</v>
       </c>
       <c r="C446" t="n">
-        <v>93.27</v>
+        <v>132.02</v>
       </c>
       <c r="D446" t="n">
-        <v>24808</v>
+        <v>25742</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
-        <v>112.4</v>
+        <v>160.76</v>
       </c>
       <c r="B447" t="n">
-        <v>25537</v>
+        <v>30105</v>
       </c>
       <c r="C447" t="n">
-        <v>115.09</v>
+        <v>150.92</v>
       </c>
       <c r="D447" t="n">
-        <v>28058</v>
+        <v>10263</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="n">
-        <v>114.29</v>
+        <v>160.86</v>
       </c>
       <c r="B448" t="n">
-        <v>23361</v>
+        <v>31325</v>
       </c>
       <c r="C448" t="n">
-        <v>113.54</v>
+        <v>180</v>
       </c>
       <c r="D448" t="n">
-        <v>28574</v>
+        <v>23738</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
-        <v>92.28</v>
+        <v>161.4</v>
       </c>
       <c r="B449" t="n">
-        <v>27604</v>
+        <v>31660</v>
       </c>
       <c r="C449" t="n">
-        <v>90.41</v>
+        <v>142.55</v>
       </c>
       <c r="D449" t="n">
-        <v>15155</v>
+        <v>10079</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
-        <v>73.28</v>
+        <v>161.41</v>
       </c>
       <c r="B450" t="n">
-        <v>23556</v>
+        <v>29899</v>
       </c>
       <c r="C450" t="n">
-        <v>73.77</v>
+        <v>174.05</v>
       </c>
       <c r="D450" t="n">
-        <v>26040</v>
+        <v>11698</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="n">
-        <v>105.59</v>
+        <v>161.65</v>
       </c>
       <c r="B451" t="n">
-        <v>44340</v>
+        <v>28807</v>
       </c>
       <c r="C451" t="n">
-        <v>106.49</v>
+        <v>180</v>
       </c>
       <c r="D451" t="n">
-        <v>25718</v>
+        <v>10761</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="n">
-        <v>82.61</v>
+        <v>162.26</v>
       </c>
       <c r="B452" t="n">
-        <v>25662</v>
+        <v>30121</v>
       </c>
       <c r="C452" t="n">
-        <v>82.56</v>
+        <v>174.87</v>
       </c>
       <c r="D452" t="n">
-        <v>28894</v>
+        <v>20362</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="n">
-        <v>111.79</v>
+        <v>162.52</v>
       </c>
       <c r="B453" t="n">
-        <v>25577</v>
+        <v>29604</v>
       </c>
       <c r="C453" t="n">
-        <v>110.44</v>
+        <v>137.82</v>
       </c>
       <c r="D453" t="n">
-        <v>17815</v>
+        <v>21780</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="n">
-        <v>102.62</v>
+        <v>162.55</v>
       </c>
       <c r="B454" t="n">
-        <v>45823</v>
+        <v>30504</v>
       </c>
       <c r="C454" t="n">
-        <v>101.81</v>
+        <v>168.99</v>
       </c>
       <c r="D454" t="n">
-        <v>17854</v>
+        <v>21524</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="n">
-        <v>107.06</v>
+        <v>162.87</v>
       </c>
       <c r="B455" t="n">
-        <v>41367</v>
+        <v>28928</v>
       </c>
       <c r="C455" t="n">
-        <v>105.89</v>
+        <v>138.67</v>
       </c>
       <c r="D455" t="n">
-        <v>23705</v>
+        <v>16016</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="n">
-        <v>97.2</v>
+        <v>162.89</v>
       </c>
       <c r="B456" t="n">
-        <v>36261</v>
+        <v>29965</v>
       </c>
       <c r="C456" t="n">
-        <v>100.67</v>
+        <v>174.69</v>
       </c>
       <c r="D456" t="n">
-        <v>28515</v>
+        <v>11128</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="n">
-        <v>98.16</v>
+        <v>163.2</v>
       </c>
       <c r="B457" t="n">
-        <v>39066</v>
+        <v>30018</v>
       </c>
       <c r="C457" t="n">
-        <v>95.04000000000001</v>
+        <v>154.88</v>
       </c>
       <c r="D457" t="n">
-        <v>28913</v>
+        <v>16441</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="n">
-        <v>79.77</v>
+        <v>164.82</v>
       </c>
       <c r="B458" t="n">
-        <v>24080</v>
+        <v>29432</v>
       </c>
       <c r="C458" t="n">
-        <v>77.26000000000001</v>
+        <v>157.58</v>
       </c>
       <c r="D458" t="n">
-        <v>29868</v>
+        <v>24233</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="n">
-        <v>101.58</v>
+        <v>164.86</v>
       </c>
       <c r="B459" t="n">
-        <v>48119</v>
+        <v>27050</v>
       </c>
       <c r="C459" t="n">
-        <v>101.81</v>
+        <v>135.19</v>
       </c>
       <c r="D459" t="n">
-        <v>29834</v>
+        <v>16033</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="n">
-        <v>92.06</v>
+        <v>164.98</v>
       </c>
       <c r="B460" t="n">
-        <v>25754</v>
+        <v>29596</v>
       </c>
       <c r="C460" t="n">
-        <v>94.37</v>
+        <v>173.78</v>
       </c>
       <c r="D460" t="n">
-        <v>21450</v>
+        <v>23163</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="n">
-        <v>91.98</v>
+        <v>165.42</v>
       </c>
       <c r="B461" t="n">
-        <v>25511</v>
+        <v>25952</v>
       </c>
       <c r="C461" t="n">
-        <v>88.92</v>
+        <v>147.98</v>
       </c>
       <c r="D461" t="n">
-        <v>17704</v>
+        <v>25200</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="n">
-        <v>99.23999999999999</v>
+        <v>165.87</v>
       </c>
       <c r="B462" t="n">
-        <v>43090</v>
+        <v>26429</v>
       </c>
       <c r="C462" t="n">
-        <v>96.45999999999999</v>
+        <v>172.27</v>
       </c>
       <c r="D462" t="n">
-        <v>10044</v>
+        <v>24407</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="n">
-        <v>98.90000000000001</v>
+        <v>166.53</v>
       </c>
       <c r="B463" t="n">
-        <v>41736</v>
+        <v>26598</v>
       </c>
       <c r="C463" t="n">
-        <v>101.84</v>
+        <v>172.15</v>
       </c>
       <c r="D463" t="n">
-        <v>24671</v>
+        <v>11598</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="n">
-        <v>144.74</v>
+        <v>166.71</v>
       </c>
       <c r="B464" t="n">
-        <v>23012</v>
+        <v>24472</v>
       </c>
       <c r="C464" t="n">
-        <v>142.72</v>
+        <v>130.65</v>
       </c>
       <c r="D464" t="n">
-        <v>10928</v>
+        <v>27378</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="n">
-        <v>93.97</v>
+        <v>166.9</v>
       </c>
       <c r="B465" t="n">
-        <v>31853</v>
+        <v>24404</v>
       </c>
       <c r="C465" t="n">
-        <v>94.48</v>
+        <v>155.31</v>
       </c>
       <c r="D465" t="n">
-        <v>28655</v>
+        <v>23804</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="n">
-        <v>111.74</v>
+        <v>167.05</v>
       </c>
       <c r="B466" t="n">
-        <v>27105</v>
+        <v>25945</v>
       </c>
       <c r="C466" t="n">
-        <v>113.85</v>
+        <v>180</v>
       </c>
       <c r="D466" t="n">
-        <v>10355</v>
+        <v>18102</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="n">
-        <v>105.38</v>
+        <v>167.93</v>
       </c>
       <c r="B467" t="n">
-        <v>43137</v>
+        <v>26933</v>
       </c>
       <c r="C467" t="n">
-        <v>108.82</v>
+        <v>177.28</v>
       </c>
       <c r="D467" t="n">
-        <v>24947</v>
+        <v>24486</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="n">
-        <v>108.12</v>
+        <v>168.34</v>
       </c>
       <c r="B468" t="n">
-        <v>39171</v>
+        <v>24331</v>
       </c>
       <c r="C468" t="n">
-        <v>107.9</v>
+        <v>145.73</v>
       </c>
       <c r="D468" t="n">
-        <v>19382</v>
+        <v>10685</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="n">
-        <v>111.89</v>
+        <v>168.74</v>
       </c>
       <c r="B469" t="n">
-        <v>26439</v>
+        <v>26548</v>
       </c>
       <c r="C469" t="n">
-        <v>112.76</v>
+        <v>152.45</v>
       </c>
       <c r="D469" t="n">
-        <v>24739</v>
+        <v>27749</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="n">
-        <v>41.5</v>
+        <v>168.91</v>
       </c>
       <c r="B470" t="n">
-        <v>26632</v>
+        <v>22760</v>
       </c>
       <c r="C470" t="n">
-        <v>41.7</v>
+        <v>179.41</v>
       </c>
       <c r="D470" t="n">
-        <v>19731</v>
+        <v>21663</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="n">
-        <v>112.94</v>
+        <v>169.31</v>
       </c>
       <c r="B471" t="n">
-        <v>24142</v>
+        <v>21453</v>
       </c>
       <c r="C471" t="n">
-        <v>113.85</v>
+        <v>180</v>
       </c>
       <c r="D471" t="n">
-        <v>28823</v>
+        <v>24704</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="n">
-        <v>100.92</v>
+        <v>169.32</v>
       </c>
       <c r="B472" t="n">
-        <v>46876</v>
+        <v>24486</v>
       </c>
       <c r="C472" t="n">
-        <v>103.26</v>
+        <v>180</v>
       </c>
       <c r="D472" t="n">
-        <v>29269</v>
+        <v>20844</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="n">
-        <v>100.92</v>
+        <v>169.63</v>
       </c>
       <c r="B473" t="n">
-        <v>46010</v>
+        <v>22946</v>
       </c>
       <c r="C473" t="n">
-        <v>98.06</v>
+        <v>145.6</v>
       </c>
       <c r="D473" t="n">
-        <v>15648</v>
+        <v>23874</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="n">
-        <v>110.53</v>
+        <v>169.8</v>
       </c>
       <c r="B474" t="n">
-        <v>32106</v>
+        <v>24789</v>
       </c>
       <c r="C474" t="n">
-        <v>110.19</v>
+        <v>137.33</v>
       </c>
       <c r="D474" t="n">
-        <v>13748</v>
+        <v>10473</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="n">
-        <v>110.35</v>
+        <v>169.97</v>
       </c>
       <c r="B475" t="n">
-        <v>32821</v>
+        <v>22649</v>
       </c>
       <c r="C475" t="n">
-        <v>109.47</v>
+        <v>180</v>
       </c>
       <c r="D475" t="n">
-        <v>15129</v>
+        <v>22277</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="n">
-        <v>30.88</v>
+        <v>170.21</v>
       </c>
       <c r="B476" t="n">
-        <v>23860</v>
+        <v>23430</v>
       </c>
       <c r="C476" t="n">
-        <v>29.98</v>
+        <v>180</v>
       </c>
       <c r="D476" t="n">
-        <v>14866</v>
+        <v>12353</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="n">
-        <v>105.2</v>
+        <v>170.3</v>
       </c>
       <c r="B477" t="n">
-        <v>45807</v>
+        <v>24832</v>
       </c>
       <c r="C477" t="n">
-        <v>106.83</v>
+        <v>180</v>
       </c>
       <c r="D477" t="n">
-        <v>24744</v>
+        <v>29735</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="n">
-        <v>102.83</v>
+        <v>170.39</v>
       </c>
       <c r="B478" t="n">
-        <v>45312</v>
+        <v>22543</v>
       </c>
       <c r="C478" t="n">
-        <v>104.4</v>
+        <v>167.07</v>
       </c>
       <c r="D478" t="n">
-        <v>18748</v>
+        <v>23183</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="n">
-        <v>103.38</v>
+        <v>170.76</v>
       </c>
       <c r="B479" t="n">
-        <v>48601</v>
+        <v>21121</v>
       </c>
       <c r="C479" t="n">
-        <v>104.15</v>
+        <v>180</v>
       </c>
       <c r="D479" t="n">
-        <v>18240</v>
+        <v>26665</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="n">
-        <v>91.3</v>
+        <v>170.8</v>
       </c>
       <c r="B480" t="n">
-        <v>24311</v>
+        <v>23072</v>
       </c>
       <c r="C480" t="n">
-        <v>92.98999999999999</v>
+        <v>160.18</v>
       </c>
       <c r="D480" t="n">
-        <v>18580</v>
+        <v>15675</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="n">
-        <v>172.05</v>
+        <v>171.15</v>
       </c>
       <c r="B481" t="n">
-        <v>23541</v>
+        <v>21176</v>
       </c>
       <c r="C481" t="n">
-        <v>173.88</v>
+        <v>180</v>
       </c>
       <c r="D481" t="n">
-        <v>29393</v>
+        <v>22815</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="n">
-        <v>96.86</v>
+        <v>171.21</v>
       </c>
       <c r="B482" t="n">
-        <v>37605</v>
+        <v>23663</v>
       </c>
       <c r="C482" t="n">
-        <v>93.03</v>
+        <v>158.67</v>
       </c>
       <c r="D482" t="n">
-        <v>20109</v>
+        <v>24329</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="n">
-        <v>98.22</v>
+        <v>171.65</v>
       </c>
       <c r="B483" t="n">
-        <v>38894</v>
+        <v>20959</v>
       </c>
       <c r="C483" t="n">
-        <v>98.68000000000001</v>
+        <v>157.44</v>
       </c>
       <c r="D483" t="n">
-        <v>14559</v>
+        <v>14400</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="n">
-        <v>91.06999999999999</v>
+        <v>172.41</v>
       </c>
       <c r="B484" t="n">
-        <v>26864</v>
+        <v>19762</v>
       </c>
       <c r="C484" t="n">
-        <v>95.04000000000001</v>
+        <v>180</v>
       </c>
       <c r="D484" t="n">
-        <v>13672</v>
+        <v>25775</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="n">
-        <v>112.69</v>
+        <v>172.45</v>
       </c>
       <c r="B485" t="n">
-        <v>23694</v>
+        <v>19639</v>
       </c>
       <c r="C485" t="n">
-        <v>111.88</v>
+        <v>180</v>
       </c>
       <c r="D485" t="n">
-        <v>27323</v>
+        <v>26794</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="n">
-        <v>102.21</v>
+        <v>172.54</v>
       </c>
       <c r="B486" t="n">
-        <v>45432</v>
+        <v>21771</v>
       </c>
       <c r="C486" t="n">
-        <v>102.01</v>
+        <v>180</v>
       </c>
       <c r="D486" t="n">
-        <v>16174</v>
+        <v>16536</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="n">
-        <v>105.23</v>
+        <v>173.21</v>
       </c>
       <c r="B487" t="n">
-        <v>48108</v>
+        <v>19075</v>
       </c>
       <c r="C487" t="n">
-        <v>101.96</v>
+        <v>178.83</v>
       </c>
       <c r="D487" t="n">
-        <v>19490</v>
+        <v>26696</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="n">
-        <v>108.64</v>
+        <v>173.41</v>
       </c>
       <c r="B488" t="n">
-        <v>37967</v>
+        <v>20294</v>
       </c>
       <c r="C488" t="n">
-        <v>112.16</v>
+        <v>175.77</v>
       </c>
       <c r="D488" t="n">
-        <v>21198</v>
+        <v>19723</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="n">
-        <v>107.95</v>
+        <v>173.71</v>
       </c>
       <c r="B489" t="n">
-        <v>39550</v>
+        <v>21341</v>
       </c>
       <c r="C489" t="n">
-        <v>108.42</v>
+        <v>180</v>
       </c>
       <c r="D489" t="n">
-        <v>29573</v>
+        <v>19304</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="n">
-        <v>111.85</v>
+        <v>175.12</v>
       </c>
       <c r="B490" t="n">
-        <v>30535</v>
+        <v>18893</v>
       </c>
       <c r="C490" t="n">
-        <v>111.65</v>
+        <v>173.63</v>
       </c>
       <c r="D490" t="n">
-        <v>12116</v>
+        <v>24527</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="n">
-        <v>110.52</v>
+        <v>175.39</v>
       </c>
       <c r="B491" t="n">
-        <v>31868</v>
+        <v>19876</v>
       </c>
       <c r="C491" t="n">
-        <v>113.61</v>
+        <v>142.84</v>
       </c>
       <c r="D491" t="n">
-        <v>20464</v>
+        <v>18026</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="n">
-        <v>102.27</v>
+        <v>176.66</v>
       </c>
       <c r="B492" t="n">
-        <v>48483</v>
+        <v>19015</v>
       </c>
       <c r="C492" t="n">
-        <v>105.22</v>
+        <v>162.85</v>
       </c>
       <c r="D492" t="n">
-        <v>15694</v>
+        <v>12523</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="n">
-        <v>110</v>
+        <v>176.83</v>
       </c>
       <c r="B493" t="n">
-        <v>34206</v>
+        <v>18166</v>
       </c>
       <c r="C493" t="n">
-        <v>114.7</v>
+        <v>180</v>
       </c>
       <c r="D493" t="n">
-        <v>16669</v>
+        <v>25602</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="n">
-        <v>101.21</v>
+        <v>176.85</v>
       </c>
       <c r="B494" t="n">
-        <v>45635</v>
+        <v>18932</v>
       </c>
       <c r="C494" t="n">
-        <v>97.59999999999999</v>
+        <v>149.5</v>
       </c>
       <c r="D494" t="n">
-        <v>27250</v>
+        <v>22797</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="n">
-        <v>150.99</v>
+        <v>177.4</v>
       </c>
       <c r="B495" t="n">
-        <v>20706</v>
+        <v>18722</v>
       </c>
       <c r="C495" t="n">
-        <v>148.95</v>
+        <v>145.86</v>
       </c>
       <c r="D495" t="n">
-        <v>19101</v>
+        <v>27585</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="n">
-        <v>51.05</v>
+        <v>177.49</v>
       </c>
       <c r="B496" t="n">
-        <v>24963</v>
+        <v>20487</v>
       </c>
       <c r="C496" t="n">
-        <v>52.57</v>
+        <v>180</v>
       </c>
       <c r="D496" t="n">
-        <v>27744</v>
+        <v>24967</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="n">
-        <v>102.2</v>
+        <v>177.68</v>
       </c>
       <c r="B497" t="n">
-        <v>46027</v>
+        <v>18233</v>
       </c>
       <c r="C497" t="n">
-        <v>101.21</v>
+        <v>180</v>
       </c>
       <c r="D497" t="n">
-        <v>23662</v>
+        <v>28453</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="n">
-        <v>95.43000000000001</v>
+        <v>177.89</v>
       </c>
       <c r="B498" t="n">
-        <v>34052</v>
+        <v>17435</v>
       </c>
       <c r="C498" t="n">
-        <v>96.02</v>
+        <v>180</v>
       </c>
       <c r="D498" t="n">
-        <v>26894</v>
+        <v>15979</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="n">
-        <v>114.58</v>
+        <v>178.91</v>
       </c>
       <c r="B499" t="n">
-        <v>22431</v>
+        <v>19469</v>
       </c>
       <c r="C499" t="n">
-        <v>118.16</v>
+        <v>166.25</v>
       </c>
       <c r="D499" t="n">
-        <v>14870</v>
+        <v>14685</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="n">
-        <v>91.33</v>
+        <v>179.06</v>
       </c>
       <c r="B500" t="n">
-        <v>24780</v>
+        <v>18412</v>
       </c>
       <c r="C500" t="n">
-        <v>88.59999999999999</v>
+        <v>180</v>
       </c>
       <c r="D500" t="n">
-        <v>27733</v>
+        <v>13230</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="n">
-        <v>108.85</v>
+        <v>179.33</v>
       </c>
       <c r="B501" t="n">
-        <v>33636</v>
+        <v>19905</v>
       </c>
       <c r="C501" t="n">
-        <v>106.25</v>
+        <v>180</v>
       </c>
       <c r="D501" t="n">
-        <v>20132</v>
+        <v>16108</v>
       </c>
     </row>
   </sheetData>
